--- a/web/veri/vetolar.xlsx
+++ b/web/veri/vetolar.xlsx
@@ -1141,12 +1141,12 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor. | Oy dağılımı: Aynı gün üç üyelik vetosu; ülke adına göre eşleştirildi (scprocedure #8).</t>
+          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor. | Oy dağılımı: Aynı gün üç üyelik vetosu; ülke adına göre eşleştirildi (Tablo 4, #8).</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | The draft was not issued as a separate document; the proposal appears in the meeting record. | Vote breakdown: Three membership vetoes on the same day; matched by country name (scprocedure #8).</t>
+          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | The draft was not issued as a separate document; the proposal appears in the meeting record. | Vote breakdown: Three membership vetoes on the same day; matched by country name (Table 4, #8).</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor. | Oy dağılımı: Aynı gün üç üyelik vetosu; ülke adına göre eşleştirildi (scprocedure #7).</t>
+          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor. | Oy dağılımı: Aynı gün üç üyelik vetosu; ülke adına göre eşleştirildi (Tablo 4, #7).</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | The draft was not issued as a separate document; the proposal appears in the meeting record. | Vote breakdown: Three membership vetoes on the same day; matched by country name (scprocedure #7).</t>
+          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | The draft was not issued as a separate document; the proposal appears in the meeting record. | Vote breakdown: Three membership vetoes on the same day; matched by country name (Table 4, #7).</t>
         </is>
       </c>
     </row>
@@ -1323,12 +1323,12 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor. | Oy dağılımı: Aynı gün üç üyelik vetosu; ülke adına göre eşleştirildi (scprocedure #6).</t>
+          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor. | Oy dağılımı: Aynı gün üç üyelik vetosu; ülke adına göre eşleştirildi (Tablo 4, #6).</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | The draft was not issued as a separate document; the proposal appears in the meeting record. | Vote breakdown: Three membership vetoes on the same day; matched by country name (scprocedure #6).</t>
+          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | The draft was not issued as a separate document; the proposal appears in the meeting record. | Vote breakdown: Three membership vetoes on the same day; matched by country name (Table 4, #6).</t>
         </is>
       </c>
     </row>
@@ -1687,12 +1687,12 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor. | Oy dağılımı: Aynı gün üç üyelik vetosu; ülke adına göre eşleştirildi (scprocedure #14).</t>
+          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor. | Oy dağılımı: Aynı gün üç üyelik vetosu; ülke adına göre eşleştirildi (Tablo 4, #14).</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | The draft was not issued as a separate document; the proposal appears in the meeting record. | Vote breakdown: Three membership vetoes on the same day; matched by country name (scprocedure #14).</t>
+          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | The draft was not issued as a separate document; the proposal appears in the meeting record. | Vote breakdown: Three membership vetoes on the same day; matched by country name (Table 4, #14).</t>
         </is>
       </c>
     </row>
@@ -1778,12 +1778,12 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor. | Oy dağılımı: Aynı gün üç üyelik vetosu; ülke adına göre eşleştirildi (scprocedure #13).</t>
+          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor. | Oy dağılımı: Aynı gün üç üyelik vetosu; ülke adına göre eşleştirildi (Tablo 4, #13).</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | The draft was not issued as a separate document; the proposal appears in the meeting record. | Vote breakdown: Three membership vetoes on the same day; matched by country name (scprocedure #13).</t>
+          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | The draft was not issued as a separate document; the proposal appears in the meeting record. | Vote breakdown: Three membership vetoes on the same day; matched by country name (Table 4, #13).</t>
         </is>
       </c>
     </row>
@@ -1869,12 +1869,12 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor. | Oy dağılımı: Aynı gün üç üyelik vetosu; ülke adına göre eşleştirildi (scprocedure #12).</t>
+          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor. | Oy dağılımı: Aynı gün üç üyelik vetosu; ülke adına göre eşleştirildi (Tablo 4, #12).</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | The draft was not issued as a separate document; the proposal appears in the meeting record. | Vote breakdown: Three membership vetoes on the same day; matched by country name (scprocedure #12).</t>
+          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | The draft was not issued as a separate document; the proposal appears in the meeting record. | Vote breakdown: Three membership vetoes on the same day; matched by country name (Table 4, #12).</t>
         </is>
       </c>
     </row>
@@ -2152,12 +2152,12 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor. | Oy dağılımı: Aynı gün iki üyelik vetosu; ülke adına göre eşleştirildi (scprocedure #18).</t>
+          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor. | Oy dağılımı: Aynı gün iki üyelik vetosu; ülke adına göre eşleştirildi (Tablo 4, #18).</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | The draft was not issued as a separate document; the proposal appears in the meeting record. | Vote breakdown: Two membership vetoes on the same day; matched by country name (scprocedure #18).</t>
+          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | The draft was not issued as a separate document; the proposal appears in the meeting record. | Vote breakdown: Two membership vetoes on the same day; matched by country name (Table 4, #18).</t>
         </is>
       </c>
     </row>
@@ -2243,12 +2243,12 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor. | Oy dağılımı: Aynı gün iki üyelik vetosu; ülke adına göre eşleştirildi (scprocedure #17).</t>
+          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor. | Oy dağılımı: Aynı gün iki üyelik vetosu; ülke adına göre eşleştirildi (Tablo 4, #17).</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | The draft was not issued as a separate document; the proposal appears in the meeting record. | Vote breakdown: Two membership vetoes on the same day; matched by country name (scprocedure #17).</t>
+          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | The draft was not issued as a separate document; the proposal appears in the meeting record. | Vote breakdown: Two membership vetoes on the same day; matched by country name (Table 4, #17).</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor. | Oy dağılımı: scprocedure dipnot 9: esas taslağa yönelik ikinci veto (#26) (scprocedure #26).</t>
+          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor. | Oy dağılımı: Referans tablonun 9. dipnotuna göre esas taslağa yönelik ikinci veto (Tablo 4, #26).</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | The draft was not issued as a separate document; the proposal appears in the meeting record. | Vote breakdown: scprocedure footnote 9: second veto, on the substantive draft (#26) (scprocedure #26).</t>
+          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | The draft was not issued as a separate document; the proposal appears in the meeting record. | Vote breakdown: According to footnote 9 of the reference table, the second veto, on the substantive draft (Table 4, #26).</t>
         </is>
       </c>
     </row>
@@ -2981,12 +2981,12 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor. | Ön soru vetosu: konunun usul meselesi sayılıp sayılmayacağına dair oylama (çifte veto). | Oy dağılımı: scprocedure dipnot 9: bu toplantıdaki ilk veto ön soru vetosudur (#25) (scprocedure #25).</t>
+          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor. | Ön soru vetosu: konunun usul meselesi sayılıp sayılmayacağına dair oylama (çifte veto). | Oy dağılımı: Referans tablonun 9. dipnotuna göre bu toplantıdaki ilk veto ön soru vetosudur (Tablo 4, #25).</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | The draft was not issued as a separate document; the proposal appears in the meeting record. | Preliminary-question veto: vote on whether the matter is to be considered procedural (double veto). | Vote breakdown: scprocedure footnote 9: the first veto at this meeting is a preliminary-question veto (#25) (scprocedure #25).</t>
+          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | The draft was not issued as a separate document; the proposal appears in the meeting record. | Preliminary-question veto: vote on whether the matter is to be considered procedural (double veto). | Vote breakdown: According to footnote 9 of the reference table, the first veto at this meeting is a preliminary-question veto (Table 4, #25).</t>
         </is>
       </c>
     </row>
@@ -4648,12 +4648,12 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | Oy dağılımı 9-2-0: S/PV.456 PDF s. 36: Kanada taslağı S/1431 Arjantin'in isteğiyle iki parça hâlinde oylandı; son paragraf dışındaki bölüm 9 lehte, 2 aleyhte (Ukrayna SSC, SSCB). Referans tablo bu vetoya da 8-2-1 veriyor; toplantı kaydında Arjantin bu oylamada lehte. DHL'deki iki satır birbirinin aynısı; kimlikler toplantıdaki oylama sırasına göre bağlandı. | scprocedure Tablo 4 #43 oy dağılımını 8-2-1 veriyor; toplantı kaydı esas alındı.</t>
+          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | Oy dağılımı 9-2-0: S/PV.456 PDF s. 36: Kanada taslağı S/1431 Arjantin'in isteğiyle iki parça hâlinde oylandı; son paragraf dışındaki bölüm 9 lehte, 2 aleyhte (Ukrayna SSC, SSCB). Referans tablo bu vetoya da 8-2-1 veriyor; toplantı kaydında Arjantin bu oylamada lehte. DHL'deki iki satır birbirinin aynısı; kimlikler toplantıdaki oylama sırasına göre bağlandı. | Referans tablo (Tablo 4, #43) oy dağılımını 8-2-1 veriyor; toplantı kaydı esas alındı.</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | Vote breakdown 9-2-0: S/PV.456 PDF p. 36: the Canadian draft S/1431 was voted on in two parts at the request of Argentina; the part other than the last paragraph 9 in favour, 2 against (Ukrainian SSR, USSR). The reference table also gives 8-2-1 for this veto; in the meeting record Argentina voted in favour in this vote. The two lines in the DHL list are identical; the identifiers were assigned in the order of the votes at the meeting. | scprocedure Table 4 #43 gives the vote breakdown as 8-2-1; the meeting record was followed.</t>
+          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | Vote breakdown 9-2-0: S/PV.456 PDF p. 36: the Canadian draft S/1431 was voted on in two parts at the request of Argentina; the part other than the last paragraph 9 in favour, 2 against (Ukrainian SSR, USSR). The reference table also gives 8-2-1 for this veto; in the meeting record Argentina voted in favour in this vote. The two lines in the DHL list are identical; the identifiers were assigned in the order of the votes at the meeting. | The reference table (Table 4, #43) gives the vote breakdown as 8-2-1; the meeting record was followed.</t>
         </is>
       </c>
     </row>
@@ -9315,12 +9315,12 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | Oy dağılımı: Aynı gün iki üyelik vetosu; ülke adına göre eşleştirildi (scprocedure #90).</t>
+          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | Oy dağılımı: Aynı gün iki üyelik vetosu; ülke adına göre eşleştirildi (Tablo 4, #90).</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | Vote breakdown: Two membership vetoes on the same day; matched by country name (scprocedure #90).</t>
+          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | Vote breakdown: Two membership vetoes on the same day; matched by country name (Table 4, #90).</t>
         </is>
       </c>
     </row>
@@ -9411,12 +9411,12 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | Oy dağılımı: Aynı gün iki üyelik vetosu; ülke adına göre eşleştirildi (scprocedure #89).</t>
+          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | Oy dağılımı: Aynı gün iki üyelik vetosu; ülke adına göre eşleştirildi (Tablo 4, #89).</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | Vote breakdown: Two membership vetoes on the same day; matched by country name (scprocedure #89).</t>
+          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | Vote breakdown: Two membership vetoes on the same day; matched by country name (Table 4, #89).</t>
         </is>
       </c>
     </row>
@@ -15334,12 +15334,12 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>Oy dağılımı: Aynı gün iki farklı gündem; konuya göre eşleştirildi (scprocedure #154).</t>
+          <t>Oy dağılımı: Aynı gün iki farklı gündem; konuya göre eşleştirildi (Tablo 4, #154).</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>Vote breakdown: Two different agenda items on the same day; matched by subject (scprocedure #154).</t>
+          <t>Vote breakdown: Two different agenda items on the same day; matched by subject (Table 4, #154).</t>
         </is>
       </c>
     </row>
@@ -15430,12 +15430,12 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>Oy dağılımı: Aynı gün iki farklı gündem; konuya göre eşleştirildi (scprocedure #153).</t>
+          <t>Oy dağılımı: Aynı gün iki farklı gündem; konuya göre eşleştirildi (Tablo 4, #153).</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>Vote breakdown: Two different agenda items on the same day; matched by subject (scprocedure #153).</t>
+          <t>Vote breakdown: Two different agenda items on the same day; matched by subject (Table 4, #153).</t>
         </is>
       </c>
     </row>
@@ -21621,12 +21621,12 @@
       </c>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>Oy dağılımı 10-1-4: S/PV.7481 PDF s. 7: S/2015/508; 10 lehte, 1 aleyhte (Rusya), 4 çekimser (Angola, Çin, Nijerya, Venezuela). | scprocedure Tablo 4 #224 oy dağılımını 11-1-4 veriyor; toplantı kaydı esas alındı.</t>
+          <t>Oy dağılımı 10-1-4: S/PV.7481 PDF s. 7: S/2015/508; 10 lehte, 1 aleyhte (Rusya), 4 çekimser (Angola, Çin, Nijerya, Venezuela). | Referans tablo (Tablo 4, #224) oy dağılımını 11-1-4 veriyor; toplantı kaydı esas alındı.</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
         <is>
-          <t>Vote breakdown 10-1-4: S/PV.7481 PDF p. 7: S/2015/508; 10 in favour, 1 against (Russia), 4 abstaining (Angola, China, Nigeria, Venezuela). | scprocedure Table 4 #224 gives the vote breakdown as 11-1-4; the meeting record was followed.</t>
+          <t>Vote breakdown 10-1-4: S/PV.7481 PDF p. 7: S/2015/508; 10 in favour, 1 against (Russia), 4 abstaining (Angola, China, Nigeria, Venezuela). | The reference table (Table 4, #224) gives the vote breakdown as 11-1-4; the meeting record was followed.</t>
         </is>
       </c>
     </row>
@@ -23265,12 +23265,12 @@
       </c>
       <c r="Z244" t="inlineStr">
         <is>
-          <t>Oy dağılımı 12-2-1: S/PV.8926 PDF s. 5: S/2021/990; 12 lehte, 2 aleyhte (Hindistan, Rusya), 1 çekimser (Çin). | scprocedure Tablo 4 #243 oy dağılımını 13-2-1 veriyor; toplantı kaydı esas alındı.</t>
+          <t>Oy dağılımı 12-2-1: S/PV.8926 PDF s. 5: S/2021/990; 12 lehte, 2 aleyhte (Hindistan, Rusya), 1 çekimser (Çin). | Referans tablo (Tablo 4, #243) oy dağılımını 13-2-1 veriyor; toplantı kaydı esas alındı.</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
         <is>
-          <t>Vote breakdown 12-2-1: S/PV.8926 PDF p. 5: S/2021/990; 12 in favour, 2 against (India, Russia), 1 abstaining (China). | scprocedure Table 4 #243 gives the vote breakdown as 13-2-1; the meeting record was followed.</t>
+          <t>Vote breakdown 12-2-1: S/PV.8926 PDF p. 5: S/2021/990; 12 in favour, 2 against (India, Russia), 1 abstaining (China). | The reference table (Table 4, #243) gives the vote breakdown as 13-2-1; the meeting record was followed.</t>
         </is>
       </c>
     </row>
@@ -25457,12 +25457,12 @@
       </c>
       <c r="Z266" t="inlineStr">
         <is>
-          <t>Oy dağılımı 11-2-2: DHL'de oy dağılımı yok, referans tablo Eylül 2025'te bitiyor. S/PV.10130 s. 4: S/2026/273 (Bahreyn, Ürdün, Kuveyt, Katar, Suudi Arabistan ve BAE taslağı, Hürmüz Boğazı) 11 lehte, 2 aleyhte (Çin, Rusya Federasyonu), 2 çekimser (Kolombiya, Pakistan). Kayıtta Başkan 'bir daimi üyenin ret oyu nedeniyle' diyor; oy listesinde iki daimi üye aleyhte. Basın bülteni SC/16330 (https://press.un.org/en/2026/sc16330.doc.htm) press.un.org CAPTCHA istediği için açılamadı; numara doğrulanamadı.</t>
+          <t>Oy dağılımı 11-2-2: DHL listesinde oy dağılımı yok, referans tablo bu tarihi kapsamıyor. S/PV.10130 s. 4: S/2026/273 (Bahreyn, Ürdün, Kuveyt, Katar, Suudi Arabistan ve BAE taslağı, Hürmüz Boğazı) 11 lehte, 2 aleyhte (Çin, Rusya Federasyonu), 2 çekimser (Kolombiya, Pakistan). Kayıtta Başkan 'bir daimi üyenin ret oyu nedeniyle' diyor; oy listesinde iki daimi üye aleyhte. Basın bülteni SC/16330 (https://press.un.org/en/2026/sc16330.doc.htm) doğrulanamadı.</t>
         </is>
       </c>
       <c r="AA266" t="inlineStr">
         <is>
-          <t>Vote breakdown 11-2-2: The DHL list has no vote breakdown; the reference table ends in September 2025. S/PV.10130 p. 4: S/2026/273 (draft by Bahrain, Jordan, Kuwait, Qatar, Saudi Arabia and the UAE, Strait of Hormuz) 11 in favour, 2 against (China, Russian Federation), 2 abstaining (Colombia, Pakistan). In the record the President refers to the negative vote of a permanent member; in the voting list two permanent members voted against. Press release SC/16330 (https://press.un.org/en/2026/sc16330.doc.htm) could not be opened because press.un.org required a CAPTCHA; the number could not be verified.</t>
+          <t>Vote breakdown 11-2-2: The DHL list has no vote breakdown and the reference table does not cover this date. S/PV.10130 p. 4: S/2026/273 (draft by Bahrain, Jordan, Kuwait, Qatar, Saudi Arabia and the UAE, Strait of Hormuz) 11 in favour, 2 against (China, Russian Federation), 2 abstaining (Colombia, Pakistan). In the record the President refers to the negative vote of a permanent member; in the voting list two permanent members voted against. Press release SC/16330 (https://press.un.org/en/2026/sc16330.doc.htm) could not be verified.</t>
         </is>
       </c>
     </row>
@@ -25578,12 +25578,12 @@
       </c>
       <c r="Z267" t="inlineStr">
         <is>
-          <t>DHL listesinde yok (10 Ekim 2026 indirmesi), referans tablo Eylül 2025'te bitiyor. S/PV.10224 s. 4: S/2026/740 (ABD taslağı) 11 lehte, 2 aleyhte (Çin, Rusya Federasyonu), 2 çekimser (Pakistan, Somali); kabul edilmedi. Taslak, 1929 (2010) sayılı kararın 29. paragrafıyla kurulan ve İran yaptırımlarını izleyen Uzmanlar Paneli'nin görevini uzatıyordu. Toplantı başında gündemin kabulü 11-2-2 usul oylamasıyla geçti (usul oylamasında veto yoktur). Basın bülteni SC/16455 (https://press.un.org/en/2026/sc16455.doc.htm) aynı sonucu veriyor.</t>
+          <t>DHL listesinde ve referans tabloda henüz yok. S/PV.10224 s. 4: S/2026/740 (ABD taslağı) 11 lehte, 2 aleyhte (Çin, Rusya Federasyonu), 2 çekimser (Pakistan, Somali); kabul edilmedi. Taslak, 1929 (2010) sayılı kararın 29. paragrafıyla kurulan ve İran yaptırımlarını izleyen Uzmanlar Paneli'nin görevini uzatıyordu. Toplantı başında gündemin kabulü 11-2-2 usul oylamasıyla geçti (usul oylamasında veto yoktur). Basın bülteni SC/16455 (https://press.un.org/en/2026/sc16455.doc.htm) aynı sonucu veriyor.</t>
         </is>
       </c>
       <c r="AA267" t="inlineStr">
         <is>
-          <t>Not in the DHL list (download of 10 October 2026); the reference table ends in September 2025. S/PV.10224 p. 4: S/2026/740 (United States draft) 11 in favour, 2 against (China, Russian Federation), 2 abstaining (Pakistan, Somalia); not adopted. The draft would have extended the mandate of the Panel of Experts established by paragraph 29 of resolution 1929 (2010) to monitor the sanctions on Iran. At the start of the meeting the agenda was adopted by a procedural vote of 11-2-2 (there is no veto in procedural votes). Press release SC/16455 (https://press.un.org/en/2026/sc16455.doc.htm) gives the same result.</t>
+          <t>Not yet in the DHL list or the reference table. S/PV.10224 p. 4: S/2026/740 (United States draft) 11 in favour, 2 against (China, Russian Federation), 2 abstaining (Pakistan, Somalia); not adopted. The draft would have extended the mandate of the Panel of Experts established by paragraph 29 of resolution 1929 (2010) to monitor the sanctions on Iran. At the start of the meeting the agenda was adopted by a procedural vote of 11-2-2 (there is no veto in procedural votes). Press release SC/16455 (https://press.un.org/en/2026/sc16455.doc.htm) gives the same result.</t>
         </is>
       </c>
     </row>

--- a/web/veri/vetolar.xlsx
+++ b/web/veri/vetolar.xlsx
@@ -8,9 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="vetolar" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sozluk" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'vetolar'!$A$1:$AA$267</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'sozluk'!$A$1:$H$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -582,7 +584,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lübnan ve Suriye heyet başkanlarının Genel Sekreter'e gönderdiği 4 Şubat 1946 tarihli mektup</t>
+          <t>Lübnan ve Suriye heyet başkanlarının Genel Sekreter’e gönderdiği 4 Şubat 1946 tarihli mektup</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -641,12 +643,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor.</t>
+          <t>Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor.</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | The draft was not issued as a separate document; the proposal appears in the meeting record.</t>
+          <t>The draft was not issued as a separate document; the proposal appears in the meeting record.</t>
         </is>
       </c>
     </row>
@@ -732,12 +734,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor.</t>
+          <t>Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor.</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | The draft was not issued as a separate document; the proposal appears in the meeting record.</t>
+          <t>The draft was not issued as a separate document; the proposal appears in the meeting record.</t>
         </is>
       </c>
     </row>
@@ -838,12 +840,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor. | Oy dağılımı 9-2-0: S/PV.49 PDF s. 14: redaksiyon komitesi çoğunluğunun hazırladığı değiştirilmiş karar taslağı; 9 lehte, 2 aleyhte (Polonya, SSCB). Günün ilk vetosu.</t>
+          <t>Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor. | Redaksiyon komitesi çoğunluğunun hazırladığı değiştirilmiş taslağa Polonya ve SSCB hayır oyu verdi. Günün ilk vetosu.</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | The draft was not issued as a separate document; the proposal appears in the meeting record. | Vote breakdown 9-2-0: S/PV.49 PDF p. 14: revised draft resolution prepared by the majority of the drafting committee; 9 in favour, 2 against (Poland, USSR). The first veto of the day.</t>
+          <t>The draft was not issued as a separate document; the proposal appears in the meeting record. | Poland and the USSR voted against the revised draft resolution prepared by the majority of the drafting committee. The first veto of the day.</t>
         </is>
       </c>
     </row>
@@ -944,12 +946,12 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor. | Ön soru vetosu: konunun usul meselesi sayılıp sayılmayacağına dair oylama (çifte veto). | Fransa'nın SSCB ile birlikte ret oyu verdiği oylama, Başkan'ın meselenin usule ilişkin olduğu yönündeki kararıdır (ön soru): S/PV.49 PDF s. 22, 8 lehte, 2 aleyhte (Fransa, SSCB), 1 çekimser (Polonya). DHL bu satırda yalnızca SSCB'yi gösteriyor. Düzeltme daha önce yanlışlıkla aynı günün ilk esas oylamasına (V-1946-06-26-1) eklenmişti. | Oy dağılımı 8-2-1: S/PV.49 PDF s. 22: Başkan'ın meselenin usule ilişkin olduğu yönündeki kararı (ön soru); 8 lehte, 2 aleyhte (Fransa, SSCB), 1 çekimser (Polonya).</t>
+          <t>Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor. | Veto, konunun usul meselesi sayılıp sayılmayacağına ilişkin ön oylamada kullanıldı; buna çifte veto denir. | DHL listesi bu satırda yalnızca SSCB’yi gösteriyor; toplantı kaydına göre Fransa da ret oyu verdi. | Başkan’ın meselenin usule ilişkin olduğu yönündeki kararı oylandı; Fransa ve SSCB hayır oyu verdi, Polonya çekimser kaldı.</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | The draft was not issued as a separate document; the proposal appears in the meeting record. | Preliminary-question veto: vote on whether the matter is to be considered procedural (double veto). | The vote in which France cast a negative vote together with the USSR is the vote on the President's ruling that the matter was procedural (preliminary question): S/PV.49 PDF p. 22, 8 in favour, 2 against (France, USSR), 1 abstaining (Poland). The DHL list shows only the USSR on this line. The correction had earlier been attached by mistake to the first substantive vote of the same day (V-1946-06-26-1). | Vote breakdown 8-2-1: S/PV.49 PDF p. 22: the President's ruling that the matter was procedural (preliminary question); 8 in favour, 2 against (France, USSR), 1 abstaining (Poland).</t>
+          <t>The draft was not issued as a separate document; the proposal appears in the meeting record. | The veto was cast in the preliminary vote on whether the matter was procedural; this is known as the double veto. | The DHL list shows only the USSR on this line; according to the meeting record, France also cast a negative vote. | The vote was on the President’s ruling that the matter was procedural; France and the USSR voted against and Poland abstained.</t>
         </is>
       </c>
     </row>
@@ -1050,12 +1052,12 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor. | Oy dağılımı 9-2-0: S/PV.49 PDF s. 47: Evatt'ın (Avustralya) karar taslağı; 9 lehte, 2 aleyhte (Polonya, SSCB). Toplantı 15.00-21.00.</t>
+          <t>Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor. | Avustralya temsilcisi Evatt’ın taslağına Polonya ve SSCB hayır oyu verdi.</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | The draft was not issued as a separate document; the proposal appears in the meeting record. | Vote breakdown 9-2-0: S/PV.49 PDF p. 47: draft resolution by Evatt (Australia); 9 in favour, 2 against (Poland, USSR). Meeting 15.00-21.00.</t>
+          <t>The draft was not issued as a separate document; the proposal appears in the meeting record. | Poland and the USSR voted against the draft resolution of Mr. Evatt of Australia.</t>
         </is>
       </c>
     </row>
@@ -1141,12 +1143,12 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor. | Oy dağılımı: Aynı gün üç üyelik vetosu; ülke adına göre eşleştirildi (Tablo 4, #8).</t>
+          <t>Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor. | O gün üç üyelik başvurusu veto edildi. Oy sayılarını referans tablodan ülke adına bakarak aldık (Tablo 4, #8).</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | The draft was not issued as a separate document; the proposal appears in the meeting record. | Vote breakdown: Three membership vetoes on the same day; matched by country name (Table 4, #8).</t>
+          <t>The draft was not issued as a separate document; the proposal appears in the meeting record. | Three membership applications were vetoed that day. We took the vote figures from the reference table by country name (Table 4, #8).</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1234,12 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor. | Oy dağılımı: Aynı gün üç üyelik vetosu; ülke adına göre eşleştirildi (Tablo 4, #7).</t>
+          <t>Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor. | O gün üç üyelik başvurusu veto edildi. Oy sayılarını referans tablodan ülke adına bakarak aldık (Tablo 4, #7).</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | The draft was not issued as a separate document; the proposal appears in the meeting record. | Vote breakdown: Three membership vetoes on the same day; matched by country name (Table 4, #7).</t>
+          <t>The draft was not issued as a separate document; the proposal appears in the meeting record. | Three membership applications were vetoed that day. We took the vote figures from the reference table by country name (Table 4, #7).</t>
         </is>
       </c>
     </row>
@@ -1323,12 +1325,12 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor. | Oy dağılımı: Aynı gün üç üyelik vetosu; ülke adına göre eşleştirildi (Tablo 4, #6).</t>
+          <t>Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor. | O gün üç üyelik başvurusu veto edildi. Oy sayılarını referans tablodan ülke adına bakarak aldık (Tablo 4, #6).</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | The draft was not issued as a separate document; the proposal appears in the meeting record. | Vote breakdown: Three membership vetoes on the same day; matched by country name (Table 4, #6).</t>
+          <t>The draft was not issued as a separate document; the proposal appears in the meeting record. | Three membership applications were vetoed that day. We took the vote figures from the reference table by country name (Table 4, #6).</t>
         </is>
       </c>
     </row>
@@ -1355,7 +1357,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ukrayna Sovyet Sosyalist Cumhuriyeti'nin Genel Sekreter'e gönderdiği 24 Ağustos 1946 tarihli telgraf</t>
+          <t>Ukrayna Sovyet Sosyalist Cumhuriyeti’nin Genel Sekreter’e gönderdiği 24 Ağustos 1946 tarihli telgraf</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1414,12 +1416,12 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor.</t>
+          <t>Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor.</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | The draft was not issued as a separate document; the proposal appears in the meeting record.</t>
+          <t>The draft was not issued as a separate document; the proposal appears in the meeting record.</t>
         </is>
       </c>
     </row>
@@ -1446,7 +1448,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korfu Boğazı'ndaki olaylar</t>
+          <t>Korfu Boğazı’ndaki olaylar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1505,12 +1507,12 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor.</t>
+          <t>Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor.</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | The draft was not issued as a separate document; the proposal appears in the meeting record.</t>
+          <t>The draft was not issued as a separate document; the proposal appears in the meeting record.</t>
         </is>
       </c>
     </row>
@@ -1596,12 +1598,12 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor.</t>
+          <t>Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor.</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | The draft was not issued as a separate document; the proposal appears in the meeting record.</t>
+          <t>The draft was not issued as a separate document; the proposal appears in the meeting record.</t>
         </is>
       </c>
     </row>
@@ -1687,12 +1689,12 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor. | Oy dağılımı: Aynı gün üç üyelik vetosu; ülke adına göre eşleştirildi (Tablo 4, #14).</t>
+          <t>Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor. | O gün üç üyelik başvurusu veto edildi. Oy sayılarını referans tablodan ülke adına bakarak aldık (Tablo 4, #14).</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | The draft was not issued as a separate document; the proposal appears in the meeting record. | Vote breakdown: Three membership vetoes on the same day; matched by country name (Table 4, #14).</t>
+          <t>The draft was not issued as a separate document; the proposal appears in the meeting record. | Three membership applications were vetoed that day. We took the vote figures from the reference table by country name (Table 4, #14).</t>
         </is>
       </c>
     </row>
@@ -1778,12 +1780,12 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor. | Oy dağılımı: Aynı gün üç üyelik vetosu; ülke adına göre eşleştirildi (Tablo 4, #13).</t>
+          <t>Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor. | O gün üç üyelik başvurusu veto edildi. Oy sayılarını referans tablodan ülke adına bakarak aldık (Tablo 4, #13).</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | The draft was not issued as a separate document; the proposal appears in the meeting record. | Vote breakdown: Three membership vetoes on the same day; matched by country name (Table 4, #13).</t>
+          <t>The draft was not issued as a separate document; the proposal appears in the meeting record. | Three membership applications were vetoed that day. We took the vote figures from the reference table by country name (Table 4, #13).</t>
         </is>
       </c>
     </row>
@@ -1869,12 +1871,12 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor. | Oy dağılımı: Aynı gün üç üyelik vetosu; ülke adına göre eşleştirildi (Tablo 4, #12).</t>
+          <t>Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor. | O gün üç üyelik başvurusu veto edildi. Oy sayılarını referans tablodan ülke adına bakarak aldık (Tablo 4, #12).</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | The draft was not issued as a separate document; the proposal appears in the meeting record. | Vote breakdown: Three membership vetoes on the same day; matched by country name (Table 4, #12).</t>
+          <t>The draft was not issued as a separate document; the proposal appears in the meeting record. | Three membership applications were vetoed that day. We took the vote figures from the reference table by country name (Table 4, #12).</t>
         </is>
       </c>
     </row>
@@ -1963,16 +1965,6 @@
           <t>kapsam_disi</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur.</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis.</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2059,16 +2051,6 @@
           <t>kapsam_disi</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur.</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis.</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2152,12 +2134,12 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor. | Oy dağılımı: Aynı gün iki üyelik vetosu; ülke adına göre eşleştirildi (Tablo 4, #18).</t>
+          <t>Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor. | O gün iki üyelik başvurusu veto edildi. Oy sayılarını referans tablodan ülke adına bakarak aldık (Tablo 4, #18).</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | The draft was not issued as a separate document; the proposal appears in the meeting record. | Vote breakdown: Two membership vetoes on the same day; matched by country name (Table 4, #18).</t>
+          <t>The draft was not issued as a separate document; the proposal appears in the meeting record. | Two membership applications were vetoed that day. We took the vote figures from the reference table by country name (Table 4, #18).</t>
         </is>
       </c>
     </row>
@@ -2243,12 +2225,12 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor. | Oy dağılımı: Aynı gün iki üyelik vetosu; ülke adına göre eşleştirildi (Tablo 4, #17).</t>
+          <t>Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor. | O gün iki üyelik başvurusu veto edildi. Oy sayılarını referans tablodan ülke adına bakarak aldık (Tablo 4, #17).</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | The draft was not issued as a separate document; the proposal appears in the meeting record. | Vote breakdown: Two membership vetoes on the same day; matched by country name (Table 4, #17).</t>
+          <t>The draft was not issued as a separate document; the proposal appears in the meeting record. | Two membership applications were vetoed that day. We took the vote figures from the reference table by country name (Table 4, #17).</t>
         </is>
       </c>
     </row>
@@ -2366,7 +2348,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Yunanistan meselesi: Kuzey Yunanistan'daki durum, ön soru</t>
+          <t>Yunanistan meselesi: Kuzey Yunanistan’daki durum, ön soru</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2430,12 +2412,12 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | Ön soru vetosu: konunun usul meselesi sayılıp sayılmayacağına dair oylama (çifte veto).</t>
+          <t>Veto, konunun usul meselesi sayılıp sayılmayacağına ilişkin ön oylamada kullanıldı; buna çifte veto denir.</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | Preliminary-question veto: vote on whether the matter is to be considered procedural (double veto).</t>
+          <t>The veto was cast in the preliminary vote on whether the matter was procedural; this is known as the double veto.</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2444,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Yunanistan meselesi: Kuzey Yunanistan'daki durum</t>
+          <t>Yunanistan meselesi: Kuzey Yunanistan’daki durum</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2524,16 +2506,6 @@
           <t>kapsam_disi</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur.</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis.</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2617,12 +2589,12 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor.</t>
+          <t>Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor.</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | The draft was not issued as a separate document; the proposal appears in the meeting record.</t>
+          <t>The draft was not issued as a separate document; the proposal appears in the meeting record.</t>
         </is>
       </c>
     </row>
@@ -2708,12 +2680,12 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor.</t>
+          <t>Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor.</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | The draft was not issued as a separate document; the proposal appears in the meeting record.</t>
+          <t>The draft was not issued as a separate document; the proposal appears in the meeting record.</t>
         </is>
       </c>
     </row>
@@ -2799,12 +2771,12 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor.</t>
+          <t>Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor.</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | The draft was not issued as a separate document; the proposal appears in the meeting record.</t>
+          <t>The draft was not issued as a separate document; the proposal appears in the meeting record.</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2803,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Şili'nin Genel Sekreter'e gönderdiği 12 Mart 1948 tarihli mektup: Çekoslovakya'daki olaylar</t>
+          <t>Şili’nin Genel Sekreter’e gönderdiği 12 Mart 1948 tarihli mektup: Çekoslovakya’daki olaylar</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2890,12 +2862,12 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor. | Oy dağılımı: Referans tablonun 9. dipnotuna göre esas taslağa yönelik ikinci veto (Tablo 4, #26).</t>
+          <t>Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor. | Referans tablonun 9. dipnotuna göre toplantının ikinci vetosu taslağın kendisine verildi (Tablo 4, #26).</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | The draft was not issued as a separate document; the proposal appears in the meeting record. | Vote breakdown: According to footnote 9 of the reference table, the second veto, on the substantive draft (Table 4, #26).</t>
+          <t>The draft was not issued as a separate document; the proposal appears in the meeting record. | Footnote 9 of the reference table identifies this as the second veto of the meeting, cast on the draft itself (Table 4, #26).</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2894,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Şili'nin Genel Sekreter'e gönderdiği 12 Mart 1948 tarihli mektup: Çekoslovakya'daki olaylar, ön soru</t>
+          <t>Şili’nin Genel Sekreter’e gönderdiği 12 Mart 1948 tarihli mektup: Çekoslovakya’daki olaylar, ön soru</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2981,12 +2953,12 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor. | Ön soru vetosu: konunun usul meselesi sayılıp sayılmayacağına dair oylama (çifte veto). | Oy dağılımı: Referans tablonun 9. dipnotuna göre bu toplantıdaki ilk veto ön soru vetosudur (Tablo 4, #25).</t>
+          <t>Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor. | Veto, konunun usul meselesi sayılıp sayılmayacağına ilişkin ön oylamada kullanıldı; buna çifte veto denir. | Referans tablonun 9. dipnotuna göre toplantının ilk vetosu ön soru vetosudur (Tablo 4, #25).</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | The draft was not issued as a separate document; the proposal appears in the meeting record. | Preliminary-question veto: vote on whether the matter is to be considered procedural (double veto). | Vote breakdown: According to footnote 9 of the reference table, the first veto at this meeting is a preliminary-question veto (Table 4, #25).</t>
+          <t>The draft was not issued as a separate document; the proposal appears in the meeting record. | The veto was cast in the preliminary vote on whether the matter was procedural; this is known as the double veto. | Footnote 9 of the reference table identifies the first veto of the meeting as the preliminary-question veto (Table 4, #25).</t>
         </is>
       </c>
     </row>
@@ -3013,7 +2985,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Atom Enerjisi Komisyonu Başkanı'nın Güvenlik Konseyi Başkanı'na Komisyonun Üçüncü Raporu'nu ileten 26 Mayıs 1948 tarihli mektubu</t>
+          <t>Atom Enerjisi Komisyonu Başkanı’nın Güvenlik Konseyi Başkanı’na Komisyonun Üçüncü Raporu’nu ileten 26 Mayıs 1948 tarihli mektubu</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -3075,16 +3047,6 @@
           <t>kapsam_disi</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur.</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis.</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3168,12 +3130,12 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor.</t>
+          <t>Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor.</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | The draft was not issued as a separate document; the proposal appears in the meeting record.</t>
+          <t>The draft was not issued as a separate document; the proposal appears in the meeting record.</t>
         </is>
       </c>
     </row>
@@ -3200,7 +3162,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fransa, Birleşik Krallık ve ABD'nin Genel Sekreter'e gönderdiği 29 Eylül 1948 tarihli özdeş bildirimler: Berlin ablukası</t>
+          <t>Fransa, Birleşik Krallık ve ABD’nin Genel Sekreter’e gönderdiği 29 Eylül 1948 tarihli özdeş bildirimler: Berlin ablukası</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -3262,16 +3224,6 @@
           <t>kapsam_disi</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur.</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis.</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3355,12 +3307,12 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor.</t>
+          <t>Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor.</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | The draft was not issued as a separate document; the proposal appears in the meeting record.</t>
+          <t>The draft was not issued as a separate document; the proposal appears in the meeting record.</t>
         </is>
       </c>
     </row>
@@ -3449,16 +3401,6 @@
           <t>kapsam_disi</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur.</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis.</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3545,16 +3487,6 @@
           <t>kapsam_disi</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur.</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis.</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3641,16 +3573,6 @@
           <t>kapsam_disi</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur.</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis.</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3737,16 +3659,6 @@
           <t>kapsam_disi</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur.</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis.</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3833,16 +3745,6 @@
           <t>kapsam_disi</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur.</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis.</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3929,16 +3831,6 @@
           <t>kapsam_disi</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur.</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis.</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4025,16 +3917,6 @@
           <t>kapsam_disi</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur.</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis.</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4121,16 +4003,6 @@
           <t>kapsam_disi</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur.</t>
-        </is>
-      </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis.</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4217,16 +4089,6 @@
           <t>kapsam_disi</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur.</t>
-        </is>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis.</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4313,16 +4175,6 @@
           <t>kapsam_disi</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur.</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis.</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4426,12 +4278,12 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | Oy dağılımı 8-2-1: S/PV.452 PDF s. 25: Fransız taslağı S/1408/Rev.1; 8 lehte, 2 aleyhte (Ukrayna SSC, SSCB), 1 çekimser (Arjantin).</t>
+          <t>Fransız taslağı S/1408/Rev.1’e Ukrayna SSC ve SSCB hayır oyu verdi; Arjantin çekimser kaldı.</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | Vote breakdown 8-2-1: S/PV.452 PDF p. 25: French draft S/1408/Rev.1; 8 in favour, 2 against (Ukrainian SSR, USSR), 1 abstaining (Argentina).</t>
+          <t>The Ukrainian SSR and the USSR voted against the French draft S/1408/Rev.1; Argentina abstained.</t>
         </is>
       </c>
     </row>
@@ -4537,12 +4389,12 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | Oy dağılımı 9-2-0: S/PV.452 PDF s. 23: Fransız taslağı S/1399/Rev.1; 9 lehte, 2 aleyhte (Ukrayna SSC, SSCB). Toplantı 15.00-18.30.</t>
+          <t>Fransız taslağı S/1399/Rev.1’e Ukrayna SSC ve SSCB hayır oyu verdi.</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | Vote breakdown 9-2-0: S/PV.452 PDF p. 23: French draft S/1399/Rev.1; 9 in favour, 2 against (Ukrainian SSR, USSR). Meeting 15.00-18.30.</t>
+          <t>The Ukrainian SSR and the USSR voted against the French draft S/1399/Rev.1.</t>
         </is>
       </c>
     </row>
@@ -4648,12 +4500,12 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | Oy dağılımı 9-2-0: S/PV.456 PDF s. 36: Kanada taslağı S/1431 Arjantin'in isteğiyle iki parça hâlinde oylandı; son paragraf dışındaki bölüm 9 lehte, 2 aleyhte (Ukrayna SSC, SSCB). Referans tablo bu vetoya da 8-2-1 veriyor; toplantı kaydında Arjantin bu oylamada lehte. DHL'deki iki satır birbirinin aynısı; kimlikler toplantıdaki oylama sırasına göre bağlandı. | Referans tablo (Tablo 4, #43) oy dağılımını 8-2-1 veriyor; toplantı kaydı esas alındı.</t>
+          <t>Kanada taslağı S/1431, Arjantin’in isteğiyle iki parça hâlinde oylandı. Son paragraf dışındaki bölüme Ukrayna SSC ve SSCB hayır oyu verdi; Arjantin bu oylamada evet oyu verdi. DHL listesi bu iki oylamayı birbirinin aynı iki satırla gösteriyor; sıralarını toplantı kaydından aldık. | Referans tablo oyu 8-2-1 veriyor; biz toplantı kaydındaki 9-2-0 sonucunu aldık (Tablo 4, #43).</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | Vote breakdown 9-2-0: S/PV.456 PDF p. 36: the Canadian draft S/1431 was voted on in two parts at the request of Argentina; the part other than the last paragraph 9 in favour, 2 against (Ukrainian SSR, USSR). The reference table also gives 8-2-1 for this veto; in the meeting record Argentina voted in favour in this vote. The two lines in the DHL list are identical; the identifiers were assigned in the order of the votes at the meeting. | The reference table (Table 4, #43) gives the vote breakdown as 8-2-1; the meeting record was followed.</t>
+          <t>The Canadian draft S/1431 was voted on in two parts at the request of Argentina. The Ukrainian SSR and the USSR voted against the part other than the last paragraph; Argentina voted in favour in this vote. The DHL list shows these two votes as identical lines; we took their order from the meeting record. | The reference table gives 8-2-1; we follow the meeting record, which gives 9-2-0 (Table 4, #43).</t>
         </is>
       </c>
     </row>
@@ -4759,12 +4611,12 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | Oy dağılımı 8-2-1: S/PV.456 PDF s. 36: S/1431'in son paragrafı ('Birleşmiş Milletler Endonezya Komisyonu'ndan ... talep eder'); 8 lehte, 2 aleyhte (Ukrayna SSC, SSCB), 1 çekimser (Arjantin). DHL'deki iki satır birbirinin aynısı; kimlikler toplantıdaki oylama sırasına göre bağlandı.</t>
+          <t>S/1431’in Birleşmiş Milletler Endonezya Komisyonuna yöneltilen son paragrafına Ukrayna SSC ve SSCB hayır oyu verdi; Arjantin çekimser kaldı. DHL listesi bu iki oylamayı birbirinin aynı iki satırla gösteriyor; sıralarını toplantı kaydından aldık.</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | Vote breakdown 8-2-1: S/PV.456 PDF p. 36: the last paragraph of S/1431 (a request addressed to the United Nations Commission for Indonesia); 8 in favour, 2 against (Ukrainian SSR, USSR), 1 abstaining (Argentina). The two lines in the DHL list are identical; the identifiers were assigned in the order of the votes at the meeting.</t>
+          <t>The Ukrainian SSR and the USSR voted against the last paragraph of S/1431, a request addressed to the United Nations Commission for Indonesia; Argentina abstained. The DHL list shows these two votes as identical lines; we took their order from the meeting record.</t>
         </is>
       </c>
     </row>
@@ -4796,7 +4648,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kore Cumhuriyeti'ne yönelik saldırı şikâyeti</t>
+          <t>Kore Cumhuriyeti’ne yönelik saldırı şikâyeti</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -4865,12 +4717,12 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | scprocedure tarihi 1950-09-06. Tarih farkı 1 gün. | DHL listesindeki tarih 1950-09-05; oylama günü toplantı kaydına göre 1950-09-06. | S/PV.496: kaydın başlığı 'Salı, 5 Eylül 1950' diyor, ancak toplantıda 6 Eylül 1950 tarihli bir mektup dağıtıldı (PDF s. 3), 495. toplantıdan 'dün' diye söz edildi (PDF s. 4; S/PV.495 5 Eylül 1950) ve toplantı 'yarın, 7 Eylül'e' ertelendi (PDF s. 22; S/PV.497 7 Eylül 1950). Toplantı 6 Eylül 1950'de 15.00-18.30 arasında yapıldı, başlıktaki tarih baskı hatası. Oylama PDF s. 19. Gece yarısı geçilmedi. Doğru tarihi referans tablo veriyor; DHL basılı başlığı izliyor.</t>
+          <t>Toplantı 6 Eylül 1950’de yapıldı; kaydın başlığındaki 5 Eylül baskı hatası (S/PV.496). Toplantıda 6 Eylül tarihli bir mektup dağıtıldı, 495. toplantıdan “dün” diye söz edildi ve toplantı “yarın, 7 Eylül” gününe ertelendi. DHL listesi başlıktaki tarihi izliyor.</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | scprocedure date 1950-09-06. Date difference 1 day. | Date in the DHL list 1950-09-05; voting day according to the meeting record 1950-09-06. | S/PV.496: the heading of the record gives Tuesday, 5 September 1950, but a letter dated 6 September 1950 was circulated at the meeting (PDF p. 3), the 495th meeting was referred to as having been held the previous day (PDF p. 4; S/PV.495 5 September 1950) and the meeting was adjourned until the next day, 7 September (PDF p. 22; S/PV.497 7 September 1950). The meeting was held on 6 September 1950 from 15.00 to 18.30; the date in the heading is a printing error. Vote PDF p. 19. Midnight was not passed. The reference table gives the correct date; DHL follows the printed heading.</t>
+          <t>The meeting was held on 6 September 1950; the date of 5 September in the heading of the record is a printing error (S/PV.496). A letter dated 6 September was circulated at the meeting, the 495th meeting was referred to as held the previous day, and the meeting was adjourned until “tomorrow, 7 September”. The DHL list follows the date in the heading.</t>
         </is>
       </c>
     </row>
@@ -4959,16 +4811,6 @@
           <t>kapsam_disi</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur.</t>
-        </is>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis.</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4993,7 +4835,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tayvan'ın (Formoza) silahlı işgali şikâyeti; Kore Cumhuriyeti'ne yönelik saldırı şikâyeti</t>
+          <t>Tayvan’ın (Formoza) silahlı işgali şikâyeti; Kore Cumhuriyeti’ne yönelik saldırı şikâyeti</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -5055,16 +4897,6 @@
           <t>kapsam_disi</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur.</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis.</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5151,16 +4983,6 @@
           <t>kapsam_disi</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur.</t>
-        </is>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis.</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5247,16 +5069,6 @@
           <t>kapsam_disi</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur.</t>
-        </is>
-      </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis.</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5343,16 +5155,6 @@
           <t>kapsam_disi</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur.</t>
-        </is>
-      </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis.</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5439,16 +5241,6 @@
           <t>kapsam_disi</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur.</t>
-        </is>
-      </c>
-      <c r="AA52" t="inlineStr">
-        <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis.</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5535,16 +5327,6 @@
           <t>kapsam_disi</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur.</t>
-        </is>
-      </c>
-      <c r="AA53" t="inlineStr">
-        <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis.</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5631,16 +5413,6 @@
           <t>kapsam_disi</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur.</t>
-        </is>
-      </c>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis.</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5727,16 +5499,6 @@
           <t>kapsam_disi</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur.</t>
-        </is>
-      </c>
-      <c r="AA55" t="inlineStr">
-        <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis.</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5823,16 +5585,6 @@
           <t>kapsam_disi</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur.</t>
-        </is>
-      </c>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis.</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5857,7 +5609,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Genel Sekreter'in atanması</t>
+          <t>Genel Sekreter’in atanması</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5907,12 +5659,12 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor. | Kapalı oturum: veto eden üye resmi bildiride yok, kaynak tarafından atfedilmiş.</t>
+          <t>Taslak ayrı belge olarak yayımlanmamış; öneri toplantı kaydında yer alıyor. | Oturum kapalıydı. Resmî bildiri veto eden üyeyi adlandırmıyor; adı DHL listesi veriyor.</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | The draft was not issued as a separate document; the proposal appears in the meeting record. | Private meeting: the vetoing member is not named in the official communiqué; the attribution is the source's.</t>
+          <t>The draft was not issued as a separate document; the proposal appears in the meeting record. | The meeting was private. The official communiqué does not name the vetoing member; the DHL list does.</t>
         </is>
       </c>
     </row>
@@ -6001,16 +5753,6 @@
           <t>kapsam_disi</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur.</t>
-        </is>
-      </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis.</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6097,16 +5839,6 @@
           <t>kapsam_disi</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur.</t>
-        </is>
-      </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis.</t>
-        </is>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -6131,7 +5863,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tayland'ın Güvenlik Konseyi Başkanı'na gönderdiği 29 Mayıs 1954 tarihli mektup</t>
+          <t>Tayland’ın Güvenlik Konseyi Başkanı’na gönderdiği 29 Mayıs 1954 tarihli mektup</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -6193,16 +5925,6 @@
           <t>kapsam_disi</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur.</t>
-        </is>
-      </c>
-      <c r="AA60" t="inlineStr">
-        <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis.</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -6227,7 +5949,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Guatemala'nın Güvenlik Konseyi Başkanı'na gönderdiği 19 Haziran 1954 tarihli telgraf</t>
+          <t>Guatemala’nın Güvenlik Konseyi Başkanı’na gönderdiği 19 Haziran 1954 tarihli telgraf</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -6289,16 +6011,6 @@
           <t>kapsam_disi</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur.</t>
-        </is>
-      </c>
-      <c r="AA61" t="inlineStr">
-        <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis.</t>
-        </is>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -6323,7 +6035,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Yeni üyelerin kabulü: karar taslağına Çin'in değişiklik önergesi</t>
+          <t>Yeni üyelerin kabulü: karar taslağına Çin’in değişiklik önergesi</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -6402,12 +6114,12 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>DHL listesinde 13 Aralık 1955 tarihli hiçbir kayıt yok. S/PV.704 par. 51 (PDF s. 12, basılı s. 10): Çin'in S/3502'ye değişiklik önergesinde (S/3506) adı geçen ilk ülkenin, Kore Cumhuriyeti'nin, listeye eklenmesi ayrı oylandı; 9 lehte, 1 aleyhte (SSCB), 1 çekimser (Yeni Zelanda). Kayıt: "That part of the amendment was not adopted, the negative vote being that of a permanent member of the Council." Toplantıdaki 16 vetonun 1.'i. Toplantı 13 Aralık 1955 Salı öğleden sonra 3'te başladı, 5.45'te bitti (PDF s. 3 ve 24). Sayfa numaraları PDF sayfasıdır (basılı sayfa = PDF sayfası - 2).</t>
+          <t>DHL listesinde bu güne ait kayıt yok; 16 vetonun hepsini toplantı kaydından ekledik. Çin’in S/3502’ye değişiklik önergesinde (S/3506) adı geçen ilk ülke, Kore Cumhuriyeti, ayrıca oylandı ve SSCB’nin ret oyu nedeniyle listeye eklenmedi; Yeni Zelanda çekimser kaldı. Toplantıdaki 16 vetonun birincisi (S/PV.704, par. 51).</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>The DHL list has no entry dated 13 December 1955. S/PV.704 para. 51 (PDF p. 12, printed p. 10): the inclusion of the first country named in the Chinese amendment to S/3502 (S/3506), the Republic of Korea, was put to a separate vote; 9 in favour, 1 against (USSR), 1 abstaining (New Zealand). The record: "That part of the amendment was not adopted, the negative vote being that of a permanent member of the Council." Veto 1 of the 16 at the meeting. The meeting opened on Tuesday, 13 December 1955 at 3 p.m. and rose at 5.45 p.m. (PDF pp. 3 and 24). Page numbers are PDF pages (printed page = PDF page - 2).</t>
+          <t>The DHL list has no entry for this day; we added all 16 vetoes from the meeting record. The first country named in China’s amendment to S/3502 (S/3506), the Republic of Korea, was put to a separate vote and was not added because of the USSR’s negative vote; New Zealand abstained. It was the first of 16 vetoes at the meeting (S/PV.704, para. 51).</t>
         </is>
       </c>
     </row>
@@ -6513,12 +6225,12 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>DHL listesinde 13 Aralık 1955 tarihli hiçbir kayıt yok. S/PV.704 par. 67 (PDF s. 15, basılı s. 13): Brezilya ve Yeni Zelanda'nın karar taslağının (S/3502) ikinci giriş paragrafındaki "Nepal" (Nepal) kelimesi ayrı oylandı; 10 lehte, 1 aleyhte (SSCB), çekimser yok. Kayıt: "The word was not adopted, the negative vote being that of a permanent member of the Council." Toplantıdaki 16 vetonun 11.'i. Toplantı 13 Aralık 1955 Salı öğleden sonra 3'te başladı, 5.45'te bitti (PDF s. 3 ve 24). Sayfa numaraları PDF sayfasıdır (basılı sayfa = PDF sayfası - 2).</t>
+          <t>Brezilya ve Yeni Zelanda taslağında (S/3502) Nepal’in adı ayrıca oylandı ve SSCB’nin ret oyu nedeniyle kabul edilmedi. Toplantıdaki 16 vetonun on birincisi (S/PV.704, par. 67).</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>The DHL list has no entry dated 13 December 1955. S/PV.704 para. 67 (PDF p. 15, printed p. 13): the word "Nepal" in the second preambular paragraph of the draft resolution of Brazil and New Zealand (S/3502) was put to a separate vote; 10 in favour, 1 against (USSR), no abstentions. The record: "The word was not adopted, the negative vote being that of a permanent member of the Council." Veto 11 of the 16 at the meeting. The meeting opened on Tuesday, 13 December 1955 at 3 p.m. and rose at 5.45 p.m. (PDF pp. 3 and 24). Page numbers are PDF pages (printed page = PDF page - 2).</t>
+          <t>The word “Nepal” in the draft of Brazil and New Zealand (S/3502) was put to a separate vote and was not adopted because of the USSR’s negative vote. It was the eleventh of 16 vetoes at the meeting (S/PV.704, para. 67).</t>
         </is>
       </c>
     </row>
@@ -6624,12 +6336,12 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>DHL listesinde 13 Aralık 1955 tarihli hiçbir kayıt yok. S/PV.704 par. 68 (PDF s. 15, basılı s. 13): Brezilya ve Yeni Zelanda'nın karar taslağının (S/3502) ikinci giriş paragrafındaki "Libya" (Libya) kelimesi ayrı oylandı; 10 lehte, 1 aleyhte (SSCB), çekimser yok. Kayıt: "The word was not adopted, the negative vote being that of a permanent member of the Council." Toplantıdaki 16 vetonun 12.'si. Toplantı 13 Aralık 1955 Salı öğleden sonra 3'te başladı, 5.45'te bitti (PDF s. 3 ve 24). Sayfa numaraları PDF sayfasıdır (basılı sayfa = PDF sayfası - 2).</t>
+          <t>Brezilya ve Yeni Zelanda taslağında (S/3502) Libya’nın adı ayrıca oylandı ve SSCB’nin ret oyu nedeniyle kabul edilmedi. Toplantıdaki 16 vetonun on ikincisi (S/PV.704, par. 68).</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>The DHL list has no entry dated 13 December 1955. S/PV.704 para. 68 (PDF p. 15, printed p. 13): the word "Libya" in the second preambular paragraph of the draft resolution of Brazil and New Zealand (S/3502) was put to a separate vote; 10 in favour, 1 against (USSR), no abstentions. The record: "The word was not adopted, the negative vote being that of a permanent member of the Council." Veto 12 of the 16 at the meeting. The meeting opened on Tuesday, 13 December 1955 at 3 p.m. and rose at 5.45 p.m. (PDF pp. 3 and 24). Page numbers are PDF pages (printed page = PDF page - 2).</t>
+          <t>The word “Libya” in the draft of Brazil and New Zealand (S/3502) was put to a separate vote and was not adopted because of the USSR’s negative vote. It was the twelfth of 16 vetoes at the meeting (S/PV.704, para. 68).</t>
         </is>
       </c>
     </row>
@@ -6735,12 +6447,12 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>DHL listesinde 13 Aralık 1955 tarihli hiçbir kayıt yok. S/PV.704 par. 69 (PDF s. 15-16, basılı s. 13-14): Brezilya ve Yeni Zelanda'nın karar taslağının (S/3502) ikinci giriş paragrafındaki "Cambodia" (Kamboçya) kelimesi ayrı oylandı; 10 lehte, 1 aleyhte (SSCB), çekimser yok. Kayıt: "The word was not adopted, the negative vote being that of a permanent member of the Council." Toplantıdaki 16 vetonun 13.'ü. Toplantı 13 Aralık 1955 Salı öğleden sonra 3'te başladı, 5.45'te bitti (PDF s. 3 ve 24). Sayfa numaraları PDF sayfasıdır (basılı sayfa = PDF sayfası - 2).</t>
+          <t>Brezilya ve Yeni Zelanda taslağında (S/3502) Kamboçya’nın adı ayrıca oylandı ve SSCB’nin ret oyu nedeniyle kabul edilmedi. Toplantıdaki 16 vetonun on üçüncüsü (S/PV.704, par. 69).</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>The DHL list has no entry dated 13 December 1955. S/PV.704 para. 69 (PDF p. 15-16, printed p. 13-14): the word "Cambodia" in the second preambular paragraph of the draft resolution of Brazil and New Zealand (S/3502) was put to a separate vote; 10 in favour, 1 against (USSR), no abstentions. The record: "The word was not adopted, the negative vote being that of a permanent member of the Council." Veto 13 of the 16 at the meeting. The meeting opened on Tuesday, 13 December 1955 at 3 p.m. and rose at 5.45 p.m. (PDF pp. 3 and 24). Page numbers are PDF pages (printed page = PDF page - 2).</t>
+          <t>The word “Cambodia” in the draft of Brazil and New Zealand (S/3502) was put to a separate vote and was not adopted because of the USSR’s negative vote. It was the thirteenth of 16 vetoes at the meeting (S/PV.704, para. 69).</t>
         </is>
       </c>
     </row>
@@ -6846,12 +6558,12 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>DHL listesinde 13 Aralık 1955 tarihli hiçbir kayıt yok. S/PV.704 par. 70 (PDF s. 16, basılı s. 14): Brezilya ve Yeni Zelanda'nın karar taslağının (S/3502) ikinci giriş paragrafındaki "Japan" (Japonya) kelimesi ayrı oylandı; 10 lehte, 1 aleyhte (SSCB), çekimser yok. Kayıt: "The word was not adopted, the negative vote being that of a permanent member of the Council." Toplantıdaki 16 vetonun 14.'ü. Toplantı 13 Aralık 1955 Salı öğleden sonra 3'te başladı, 5.45'te bitti (PDF s. 3 ve 24). Sayfa numaraları PDF sayfasıdır (basılı sayfa = PDF sayfası - 2).</t>
+          <t>Brezilya ve Yeni Zelanda taslağında (S/3502) Japonya’nın adı ayrıca oylandı ve SSCB’nin ret oyu nedeniyle kabul edilmedi. Toplantıdaki 16 vetonun on dördüncüsü (S/PV.704, par. 70).</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>The DHL list has no entry dated 13 December 1955. S/PV.704 para. 70 (PDF p. 16, printed p. 14): the word "Japan" in the second preambular paragraph of the draft resolution of Brazil and New Zealand (S/3502) was put to a separate vote; 10 in favour, 1 against (USSR), no abstentions. The record: "The word was not adopted, the negative vote being that of a permanent member of the Council." Veto 14 of the 16 at the meeting. The meeting opened on Tuesday, 13 December 1955 at 3 p.m. and rose at 5.45 p.m. (PDF pp. 3 and 24). Page numbers are PDF pages (printed page = PDF page - 2).</t>
+          <t>The word “Japan” in the draft of Brazil and New Zealand (S/3502) was put to a separate vote and was not adopted because of the USSR’s negative vote. It was the fourteenth of 16 vetoes at the meeting (S/PV.704, para. 70).</t>
         </is>
       </c>
     </row>
@@ -6957,12 +6669,12 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>DHL listesinde 13 Aralık 1955 tarihli hiçbir kayıt yok. S/PV.704 par. 71 (PDF s. 16, basılı s. 14): Brezilya ve Yeni Zelanda'nın karar taslağının (S/3502) ikinci giriş paragrafındaki "Laos" (Laos) kelimesi ayrı oylandı; 10 lehte, 1 aleyhte (SSCB), çekimser yok. Kayıt: "The word was not adopted, the negative vote being that of a permanent member of the Council." Toplantıdaki 16 vetonun 15.'i. Toplantı 13 Aralık 1955 Salı öğleden sonra 3'te başladı, 5.45'te bitti (PDF s. 3 ve 24). Sayfa numaraları PDF sayfasıdır (basılı sayfa = PDF sayfası - 2).</t>
+          <t>Brezilya ve Yeni Zelanda taslağında (S/3502) Laos’un adı ayrıca oylandı ve SSCB’nin ret oyu nedeniyle kabul edilmedi. Toplantıdaki 16 vetonun on beşincisi (S/PV.704, par. 71).</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>The DHL list has no entry dated 13 December 1955. S/PV.704 para. 71 (PDF p. 16, printed p. 14): the word "Laos" in the second preambular paragraph of the draft resolution of Brazil and New Zealand (S/3502) was put to a separate vote; 10 in favour, 1 against (USSR), no abstentions. The record: "The word was not adopted, the negative vote being that of a permanent member of the Council." Veto 15 of the 16 at the meeting. The meeting opened on Tuesday, 13 December 1955 at 3 p.m. and rose at 5.45 p.m. (PDF pp. 3 and 24). Page numbers are PDF pages (printed page = PDF page - 2).</t>
+          <t>The word “Laos” in the draft of Brazil and New Zealand (S/3502) was put to a separate vote and was not adopted because of the USSR’s negative vote. It was the fifteenth of 16 vetoes at the meeting (S/PV.704, para. 71).</t>
         </is>
       </c>
     </row>
@@ -7068,12 +6780,12 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>DHL listesinde 13 Aralık 1955 tarihli hiçbir kayıt yok. S/PV.704 par. 72 (PDF s. 16, basılı s. 14): Brezilya ve Yeni Zelanda'nın karar taslağının (S/3502) ikinci giriş paragrafındaki "Spain" (İspanya) kelimesi ayrı oylandı; 9 lehte, 1 aleyhte (SSCB), 1 çekimser (Belçika). Kayıt: "The word was not adopted, the negative vote being that of a permanent member of the Council." Toplantıdaki 16 vetonun 16.'sı. Toplantı 13 Aralık 1955 Salı öğleden sonra 3'te başladı, 5.45'te bitti (PDF s. 3 ve 24). Sayfa numaraları PDF sayfasıdır (basılı sayfa = PDF sayfası - 2).</t>
+          <t>Brezilya ve Yeni Zelanda taslağında (S/3502) İspanya’nın adı ayrıca oylandı ve SSCB’nin ret oyu nedeniyle kabul edilmedi; Belçika çekimser kaldı. Toplantıdaki 16 vetonun on altıncısı (S/PV.704, par. 72).</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>The DHL list has no entry dated 13 December 1955. S/PV.704 para. 72 (PDF p. 16, printed p. 14): the word "Spain" in the second preambular paragraph of the draft resolution of Brazil and New Zealand (S/3502) was put to a separate vote; 9 in favour, 1 against (USSR), 1 abstaining (Belgium). The record: "The word was not adopted, the negative vote being that of a permanent member of the Council." Veto 16 of the 16 at the meeting. The meeting opened on Tuesday, 13 December 1955 at 3 p.m. and rose at 5.45 p.m. (PDF pp. 3 and 24). Page numbers are PDF pages (printed page = PDF page - 2).</t>
+          <t>The word “Spain” in the draft of Brazil and New Zealand (S/3502) was put to a separate vote and was not adopted because of the USSR’s negative vote; Belgium abstained. It was the sixteenth of 16 vetoes at the meeting (S/PV.704, para. 72).</t>
         </is>
       </c>
     </row>
@@ -7179,12 +6891,12 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>DHL listesinde yok. S/PV.704 par. 54 (PDF s. 13, basılı s. 11): Brezilya ve Yeni Zelanda'nın karar taslağının (S/3502) ikinci giriş paragrafındaki "Mongolian People's Republic" (Moğolistan Halk Cumhuriyeti) sözcükleri ayrı oylandı; 8 lehte, 1 aleyhte (Çin), 2 çekimser (Belçika, ABD). Kayıt: "The words were not adopted, the negative vote being that of a permanent member of the Council." Toplantıdaki 16 vetonun 3.'sü; scprocedure Tablo 4 bu vetoyu günün son satırında (#76) veriyor. Çin koltuğu o tarihte Çin Cumhuriyeti'ndeydi (Tayvan): toplantıda Çin'i Bay Tsiang temsil ediyor; ABD temsilcisi ondan "the representative of the Republic of China" diye söz ediyor (par. 95 (PDF s. 20)); SSCB temsilcisi bu vetoyu "the veto by the Kuomintang representative" diye anıyor (par. 121 (PDF s. 23)). Toplantı 13 Aralık 1955 Salı öğleden sonra 3'te başladı, 5.45'te bitti (PDF s. 3 ve 24). Sayfa numaraları PDF sayfasıdır (basılı sayfa = PDF sayfası - 2).</t>
+          <t>Brezilya ve Yeni Zelanda taslağında (S/3502) Moğolistan Halk Cumhuriyeti’nin adı ayrıca oylandı ve Çin’in ret oyu nedeniyle kabul edilmedi; Belçika ve ABD çekimser kaldı. Toplantıdaki 16 vetonun üçüncüsü (S/PV.704, par. 54); referans tablo bu vetoyu günün son satırında veriyor (Tablo 4, #76). Çin koltuğu o tarihte Çin Cumhuriyeti’ndeydi (Tayvan). ABD temsilcisi Çin temsilcisi Bay Tsiang’dan “the representative of the Republic of China” diye söz ediyor (par. 95), SSCB temsilcisi bu vetoyu “the veto by the Kuomintang representative” diye anıyor (par. 121).</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>Not in the DHL list. S/PV.704 para. 54 (PDF p. 13, printed p. 11): the words "Mongolian People's Republic" in the second preambular paragraph of the draft resolution of Brazil and New Zealand (S/3502) were put to a separate vote; 8 in favour, 1 against (China), 2 abstaining (Belgium, United States). The record: "The words were not adopted, the negative vote being that of a permanent member of the Council." Veto 3 of the 16 at the meeting; scprocedure Table 4 lists it as the last entry of the day (No. 76). At that date China's seat was held by the Republic of China (Taiwan): China is represented at the meeting by Mr. Tsiang; the United States representative refers to him as "the representative of the Republic of China" (para. 95 (PDF p. 20)); the USSR representative calls this veto "the veto by the Kuomintang representative" (para. 121 (PDF p. 23)). The meeting opened on Tuesday, 13 December 1955 at 3 p.m. and rose at 5.45 p.m. (PDF pp. 3 and 24). Page numbers are PDF pages (printed page = PDF page - 2).</t>
+          <t>The words “Mongolian People’s Republic” in the draft of Brazil and New Zealand (S/3502) were put to a separate vote and were not adopted because of China’s negative vote; Belgium and the United States abstained. It was the third of 16 vetoes at the meeting (S/PV.704, para. 54); the reference table lists it last for the day (Table 4, #76). At that date China’s seat was held by the Republic of China (Taiwan). The United States representative refers to the Chinese representative, Mr. Tsiang, as “the representative of the Republic of China” (para. 95), and the USSR representative calls this veto “the veto by the Kuomintang representative” (para. 121).</t>
         </is>
       </c>
     </row>
@@ -7211,7 +6923,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Yeni üyelerin kabulü: karar taslağına Çin'in değişiklik önergesi</t>
+          <t>Yeni üyelerin kabulü: karar taslağına Çin’in değişiklik önergesi</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -7290,12 +7002,12 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>DHL listesinde 13 Aralık 1955 tarihli hiçbir kayıt yok. S/PV.704 par. 52 (PDF s. 12, basılı s. 10): Çin'in S/3502'ye değişiklik önergesinde (S/3506) adı geçen ikinci ülkenin, Vietnam Cumhuriyeti'nin, listeye eklenmesi ayrı oylandı; 9 lehte, 1 aleyhte (SSCB), 1 çekimser (Yeni Zelanda). Kayıt: "That part of the amendment was not adopted, the negative vote being that of a permanent member of the Council." Toplantıdaki 16 vetonun 2.'si. Toplantı 13 Aralık 1955 Salı öğleden sonra 3'te başladı, 5.45'te bitti (PDF s. 3 ve 24). Sayfa numaraları PDF sayfasıdır (basılı sayfa = PDF sayfası - 2).</t>
+          <t>Çin’in S/3502’ye değişiklik önergesinde (S/3506) adı geçen ikinci ülke, Vietnam Cumhuriyeti, ayrıca oylandı ve SSCB’nin ret oyu nedeniyle listeye eklenmedi; Yeni Zelanda çekimser kaldı. Toplantıdaki 16 vetonun ikincisi (S/PV.704, par. 52).</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>The DHL list has no entry dated 13 December 1955. S/PV.704 para. 52 (PDF p. 12, printed p. 10): the inclusion of the second country named in the Chinese amendment to S/3502 (S/3506), the Republic of Viet-Nam, was put to a separate vote; 9 in favour, 1 against (USSR), 1 abstaining (New Zealand). The record: "That part of the amendment was not adopted, the negative vote being that of a permanent member of the Council." Veto 2 of the 16 at the meeting. The meeting opened on Tuesday, 13 December 1955 at 3 p.m. and rose at 5.45 p.m. (PDF pp. 3 and 24). Page numbers are PDF pages (printed page = PDF page - 2).</t>
+          <t>The second country named in China’s amendment to S/3502 (S/3506), the Republic of Viet-Nam, was put to a separate vote and was not added because of the USSR’s negative vote; New Zealand abstained. It was the second of 16 vetoes at the meeting (S/PV.704, para. 52).</t>
         </is>
       </c>
     </row>
@@ -7401,12 +7113,12 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>DHL listesinde 13 Aralık 1955 tarihli hiçbir kayıt yok. S/PV.704 par. 57 (PDF s. 13, basılı s. 11): Brezilya ve Yeni Zelanda'nın karar taslağının (S/3502) ikinci giriş paragrafındaki "Jordan" (Ürdün) kelimesi ayrı oylandı; 10 lehte, 1 aleyhte (SSCB), çekimser yok. Kayıt: "The word was not adopted, the negative vote being that of a permanent member of the Council." Toplantıdaki 16 vetonun 4.'ü. Toplantı 13 Aralık 1955 Salı öğleden sonra 3'te başladı, 5.45'te bitti (PDF s. 3 ve 24). Sayfa numaraları PDF sayfasıdır (basılı sayfa = PDF sayfası - 2).</t>
+          <t>Brezilya ve Yeni Zelanda taslağında (S/3502) Ürdün’ün adı ayrıca oylandı ve SSCB’nin ret oyu nedeniyle kabul edilmedi. Toplantıdaki 16 vetonun dördüncüsü (S/PV.704, par. 57).</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>The DHL list has no entry dated 13 December 1955. S/PV.704 para. 57 (PDF p. 13, printed p. 11): the word "Jordan" in the second preambular paragraph of the draft resolution of Brazil and New Zealand (S/3502) was put to a separate vote; 10 in favour, 1 against (USSR), no abstentions. The record: "The word was not adopted, the negative vote being that of a permanent member of the Council." Veto 4 of the 16 at the meeting. The meeting opened on Tuesday, 13 December 1955 at 3 p.m. and rose at 5.45 p.m. (PDF pp. 3 and 24). Page numbers are PDF pages (printed page = PDF page - 2).</t>
+          <t>The word “Jordan” in the draft of Brazil and New Zealand (S/3502) was put to a separate vote and was not adopted because of the USSR’s negative vote. It was the fourth of 16 vetoes at the meeting (S/PV.704, para. 57).</t>
         </is>
       </c>
     </row>
@@ -7512,12 +7224,12 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>DHL listesinde 13 Aralık 1955 tarihli hiçbir kayıt yok. S/PV.704 par. 58 (PDF s. 13, basılı s. 11): Brezilya ve Yeni Zelanda'nın karar taslağının (S/3502) ikinci giriş paragrafındaki "Ireland" (İrlanda) kelimesi ayrı oylandı; 10 lehte, 1 aleyhte (SSCB), çekimser yok. Kayıt: "The word was not adopted, the negative vote being that of a permanent member of the Council." Toplantıdaki 16 vetonun 5.'i. Toplantı 13 Aralık 1955 Salı öğleden sonra 3'te başladı, 5.45'te bitti (PDF s. 3 ve 24). Sayfa numaraları PDF sayfasıdır (basılı sayfa = PDF sayfası - 2).</t>
+          <t>Brezilya ve Yeni Zelanda taslağında (S/3502) İrlanda’nın adı ayrıca oylandı ve SSCB’nin ret oyu nedeniyle kabul edilmedi. Toplantıdaki 16 vetonun beşincisi (S/PV.704, par. 58).</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>The DHL list has no entry dated 13 December 1955. S/PV.704 para. 58 (PDF p. 13, printed p. 11): the word "Ireland" in the second preambular paragraph of the draft resolution of Brazil and New Zealand (S/3502) was put to a separate vote; 10 in favour, 1 against (USSR), no abstentions. The record: "The word was not adopted, the negative vote being that of a permanent member of the Council." Veto 5 of the 16 at the meeting. The meeting opened on Tuesday, 13 December 1955 at 3 p.m. and rose at 5.45 p.m. (PDF pp. 3 and 24). Page numbers are PDF pages (printed page = PDF page - 2).</t>
+          <t>The word “Ireland” in the draft of Brazil and New Zealand (S/3502) was put to a separate vote and was not adopted because of the USSR’s negative vote. It was the fifth of 16 vetoes at the meeting (S/PV.704, para. 58).</t>
         </is>
       </c>
     </row>
@@ -7623,12 +7335,12 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>DHL listesinde 13 Aralık 1955 tarihli hiçbir kayıt yok. S/PV.704 par. 59 (PDF s. 13-14, basılı s. 11-12): Brezilya ve Yeni Zelanda'nın karar taslağının (S/3502) ikinci giriş paragrafındaki "Portugal" (Portekiz) kelimesi ayrı oylandı; 10 lehte, 1 aleyhte (SSCB), çekimser yok. Kayıt: "The word was not adopted, the negative vote being that of a permanent member of the Council." Toplantıdaki 16 vetonun 6.'sı. Toplantı 13 Aralık 1955 Salı öğleden sonra 3'te başladı, 5.45'te bitti (PDF s. 3 ve 24). Sayfa numaraları PDF sayfasıdır (basılı sayfa = PDF sayfası - 2).</t>
+          <t>Brezilya ve Yeni Zelanda taslağında (S/3502) Portekiz’in adı ayrıca oylandı ve SSCB’nin ret oyu nedeniyle kabul edilmedi. Toplantıdaki 16 vetonun altıncısı (S/PV.704, par. 59).</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>The DHL list has no entry dated 13 December 1955. S/PV.704 para. 59 (PDF p. 13-14, printed p. 11-12): the word "Portugal" in the second preambular paragraph of the draft resolution of Brazil and New Zealand (S/3502) was put to a separate vote; 10 in favour, 1 against (USSR), no abstentions. The record: "The word was not adopted, the negative vote being that of a permanent member of the Council." Veto 6 of the 16 at the meeting. The meeting opened on Tuesday, 13 December 1955 at 3 p.m. and rose at 5.45 p.m. (PDF pp. 3 and 24). Page numbers are PDF pages (printed page = PDF page - 2).</t>
+          <t>The word “Portugal” in the draft of Brazil and New Zealand (S/3502) was put to a separate vote and was not adopted because of the USSR’s negative vote. It was the sixth of 16 vetoes at the meeting (S/PV.704, para. 59).</t>
         </is>
       </c>
     </row>
@@ -7734,12 +7446,12 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>DHL listesinde 13 Aralık 1955 tarihli hiçbir kayıt yok. S/PV.704 par. 61 (PDF s. 14, basılı s. 12): Brezilya ve Yeni Zelanda'nın karar taslağının (S/3502) ikinci giriş paragrafındaki "Italy" (İtalya) kelimesi ayrı oylandı; 10 lehte, 1 aleyhte (SSCB), çekimser yok. Kayıt: "The word was not adopted, the negative vote being that of a permanent member of the Council." Toplantıdaki 16 vetonun 7.'si. Toplantı 13 Aralık 1955 Salı öğleden sonra 3'te başladı, 5.45'te bitti (PDF s. 3 ve 24). Sayfa numaraları PDF sayfasıdır (basılı sayfa = PDF sayfası - 2).</t>
+          <t>Brezilya ve Yeni Zelanda taslağında (S/3502) İtalya’nın adı ayrıca oylandı ve SSCB’nin ret oyu nedeniyle kabul edilmedi. Toplantıdaki 16 vetonun yedincisi (S/PV.704, par. 61).</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>The DHL list has no entry dated 13 December 1955. S/PV.704 para. 61 (PDF p. 14, printed p. 12): the word "Italy" in the second preambular paragraph of the draft resolution of Brazil and New Zealand (S/3502) was put to a separate vote; 10 in favour, 1 against (USSR), no abstentions. The record: "The word was not adopted, the negative vote being that of a permanent member of the Council." Veto 7 of the 16 at the meeting. The meeting opened on Tuesday, 13 December 1955 at 3 p.m. and rose at 5.45 p.m. (PDF pp. 3 and 24). Page numbers are PDF pages (printed page = PDF page - 2).</t>
+          <t>The word “Italy” in the draft of Brazil and New Zealand (S/3502) was put to a separate vote and was not adopted because of the USSR’s negative vote. It was the seventh of 16 vetoes at the meeting (S/PV.704, para. 61).</t>
         </is>
       </c>
     </row>
@@ -7845,12 +7557,12 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>DHL listesinde 13 Aralık 1955 tarihli hiçbir kayıt yok. S/PV.704 par. 62 (PDF s. 14, basılı s. 12): Brezilya ve Yeni Zelanda'nın karar taslağının (S/3502) ikinci giriş paragrafındaki "Austria" (Avusturya) kelimesi ayrı oylandı; 10 lehte, 1 aleyhte (SSCB), çekimser yok. Kayıt: "The word was not adopted, the negative vote being that of a permanent member of the Council." Toplantıdaki 16 vetonun 8.'i. Toplantı 13 Aralık 1955 Salı öğleden sonra 3'te başladı, 5.45'te bitti (PDF s. 3 ve 24). Sayfa numaraları PDF sayfasıdır (basılı sayfa = PDF sayfası - 2).</t>
+          <t>Brezilya ve Yeni Zelanda taslağında (S/3502) Avusturya’nın adı ayrıca oylandı ve SSCB’nin ret oyu nedeniyle kabul edilmedi. Toplantıdaki 16 vetonun sekizincisi (S/PV.704, par. 62).</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>The DHL list has no entry dated 13 December 1955. S/PV.704 para. 62 (PDF p. 14, printed p. 12): the word "Austria" in the second preambular paragraph of the draft resolution of Brazil and New Zealand (S/3502) was put to a separate vote; 10 in favour, 1 against (USSR), no abstentions. The record: "The word was not adopted, the negative vote being that of a permanent member of the Council." Veto 8 of the 16 at the meeting. The meeting opened on Tuesday, 13 December 1955 at 3 p.m. and rose at 5.45 p.m. (PDF pp. 3 and 24). Page numbers are PDF pages (printed page = PDF page - 2).</t>
+          <t>The word “Austria” in the draft of Brazil and New Zealand (S/3502) was put to a separate vote and was not adopted because of the USSR’s negative vote. It was the eighth of 16 vetoes at the meeting (S/PV.704, para. 62).</t>
         </is>
       </c>
     </row>
@@ -7956,12 +7668,12 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>DHL listesinde 13 Aralık 1955 tarihli hiçbir kayıt yok. S/PV.704 par. 65 (PDF s. 15, basılı s. 13): Brezilya ve Yeni Zelanda'nın karar taslağının (S/3502) ikinci giriş paragrafındaki "Finland" (Finlandiya) kelimesi ayrı oylandı; 10 lehte, 1 aleyhte (SSCB), çekimser yok. Kayıt: "The word was not adopted, the negative vote being that of a permanent member of the Council." Toplantıdaki 16 vetonun 9.'u. Toplantı 13 Aralık 1955 Salı öğleden sonra 3'te başladı, 5.45'te bitti (PDF s. 3 ve 24). Sayfa numaraları PDF sayfasıdır (basılı sayfa = PDF sayfası - 2).</t>
+          <t>Brezilya ve Yeni Zelanda taslağında (S/3502) Finlandiya’nın adı ayrıca oylandı ve SSCB’nin ret oyu nedeniyle kabul edilmedi. Toplantıdaki 16 vetonun dokuzuncusu (S/PV.704, par. 65).</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>The DHL list has no entry dated 13 December 1955. S/PV.704 para. 65 (PDF p. 15, printed p. 13): the word "Finland" in the second preambular paragraph of the draft resolution of Brazil and New Zealand (S/3502) was put to a separate vote; 10 in favour, 1 against (USSR), no abstentions. The record: "The word was not adopted, the negative vote being that of a permanent member of the Council." Veto 9 of the 16 at the meeting. The meeting opened on Tuesday, 13 December 1955 at 3 p.m. and rose at 5.45 p.m. (PDF pp. 3 and 24). Page numbers are PDF pages (printed page = PDF page - 2).</t>
+          <t>The word “Finland” in the draft of Brazil and New Zealand (S/3502) was put to a separate vote and was not adopted because of the USSR’s negative vote. It was the ninth of 16 vetoes at the meeting (S/PV.704, para. 65).</t>
         </is>
       </c>
     </row>
@@ -8067,12 +7779,12 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>DHL listesinde 13 Aralık 1955 tarihli hiçbir kayıt yok. S/PV.704 par. 66 (PDF s. 15, basılı s. 13): Brezilya ve Yeni Zelanda'nın karar taslağının (S/3502) ikinci giriş paragrafındaki "Ceylon" (Seylan) kelimesi ayrı oylandı; 10 lehte, 1 aleyhte (SSCB), çekimser yok. Kayıt: "The word was not adopted, the negative vote being that of a permanent member of the Council." Toplantıdaki 16 vetonun 10.'u. Toplantı 13 Aralık 1955 Salı öğleden sonra 3'te başladı, 5.45'te bitti (PDF s. 3 ve 24). Sayfa numaraları PDF sayfasıdır (basılı sayfa = PDF sayfası - 2).</t>
+          <t>Brezilya ve Yeni Zelanda taslağında (S/3502) Seylan’ın adı ayrıca oylandı ve SSCB’nin ret oyu nedeniyle kabul edilmedi. Toplantıdaki 16 vetonun onuncusu (S/PV.704, par. 66).</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>The DHL list has no entry dated 13 December 1955. S/PV.704 para. 66 (PDF p. 15, printed p. 13): the word "Ceylon" in the second preambular paragraph of the draft resolution of Brazil and New Zealand (S/3502) was put to a separate vote; 10 in favour, 1 against (USSR), no abstentions. The record: "The word was not adopted, the negative vote being that of a permanent member of the Council." Veto 10 of the 16 at the meeting. The meeting opened on Tuesday, 13 December 1955 at 3 p.m. and rose at 5.45 p.m. (PDF pp. 3 and 24). Page numbers are PDF pages (printed page = PDF page - 2).</t>
+          <t>The word “Ceylon” in the draft of Brazil and New Zealand (S/3502) was put to a separate vote and was not adopted because of the USSR’s negative vote. It was the tenth of 16 vetoes at the meeting (S/PV.704, para. 66).</t>
         </is>
       </c>
     </row>
@@ -8161,16 +7873,6 @@
           <t>kapsam_disi</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur.</t>
-        </is>
-      </c>
-      <c r="AA78" t="inlineStr">
-        <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis.</t>
-        </is>
-      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -8257,16 +7959,6 @@
           <t>kapsam_disi</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur.</t>
-        </is>
-      </c>
-      <c r="AA79" t="inlineStr">
-        <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis.</t>
-        </is>
-      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -8291,7 +7983,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mısır Hükümeti'nin, 1888 Süveyş Kanalı Sözleşmesi'yle teyit edilip tamamlanan Süveyş Kanalı'nın uluslararası işletme sistemine tek taraflı olarak son vermesiyle ortaya çıkan durum</t>
+          <t>Mısır Hükümetinin, 1888 Süveyş Kanalı Sözleşmesi’yle teyit edilip tamamlanan Süveyş Kanalı’nın uluslararası işletme sistemine tek taraflı olarak son vermesiyle ortaya çıkan durum</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -8353,16 +8045,6 @@
           <t>kapsam_disi</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur.</t>
-        </is>
-      </c>
-      <c r="AA80" t="inlineStr">
-        <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis.</t>
-        </is>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -8387,7 +8069,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>ABD'nin Güvenlik Konseyi Başkanı'na gönderdiği, Filistin meselesine ilişkin 29 Ekim 1956 tarihli mektup</t>
+          <t>ABD’nin Güvenlik Konseyi Başkanı’na gönderdiği, Filistin meselesine ilişkin 29 Ekim 1956 tarihli mektup</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -8478,7 +8160,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>ABD'nin Güvenlik Konseyi Başkanı'na gönderdiği, Filistin meselesine ilişkin 29 Ekim 1956 tarihli mektup</t>
+          <t>ABD’nin Güvenlik Konseyi Başkanı’na gönderdiği, Filistin meselesine ilişkin 29 Ekim 1956 tarihli mektup</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -8569,7 +8251,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Fransa, Birleşik Krallık ve ABD'nin Güvenlik Konseyi Başkanı'na gönderdiği, Macaristan'daki duruma ilişkin 27 Ekim 1956 tarihli mektup</t>
+          <t>Fransa, Birleşik Krallık ve ABD’nin Güvenlik Konseyi Başkanı’na gönderdiği, Macaristan’daki duruma ilişkin 27 Ekim 1956 tarihli mektup</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -8631,16 +8313,6 @@
           <t>kapsam_disi</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur.</t>
-        </is>
-      </c>
-      <c r="AA83" t="inlineStr">
-        <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis.</t>
-        </is>
-      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -8727,16 +8399,6 @@
           <t>kapsam_disi</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur.</t>
-        </is>
-      </c>
-      <c r="AA84" t="inlineStr">
-        <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis.</t>
-        </is>
-      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -8823,16 +8485,6 @@
           <t>kapsam_disi</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur.</t>
-        </is>
-      </c>
-      <c r="AA85" t="inlineStr">
-        <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis.</t>
-        </is>
-      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -8919,16 +8571,6 @@
           <t>kapsam_disi</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur.</t>
-        </is>
-      </c>
-      <c r="AA86" t="inlineStr">
-        <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis.</t>
-        </is>
-      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -8953,7 +8595,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>SSCB'nin Güvenlik Konseyi Başkanı'na gönderdiği 18 Nisan 1958 tarihli, "Atom ve hidrojen bombalarıyla donatılmış ABD askerî uçaklarının Sovyetler Birliği sınırları yönündeki uçuşlarına son verilmesi için acil önlemler" başlıklı mektupla yaptığı şikâyet</t>
+          <t>SSCB’nin Güvenlik Konseyi Başkanı’na gönderdiği 18 Nisan 1958 tarihli, “Atom ve hidrojen bombalarıyla donatılmış ABD askerî uçaklarının Sovyetler Birliği sınırları yönündeki uçuşlarına son verilmesi için acil önlemler” başlıklı mektupla yaptığı şikâyet</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -9015,16 +8657,6 @@
           <t>kapsam_disi</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur.</t>
-        </is>
-      </c>
-      <c r="AA87" t="inlineStr">
-        <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis.</t>
-        </is>
-      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -9049,7 +8681,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lübnan'ın 22 Mayıs 1958 tarihli ve Ürdün'ün 17 Temmuz 1958 tarihli Güvenlik Konseyi Başkanı'na mektupları: Lübnan ve Ürdün'ün, Birleşik Arap Cumhuriyeti'nin iç işlerine müdahalesine ilişkin şikâyetleri</t>
+          <t>Lübnan’ın 22 Mayıs 1958 tarihli ve Ürdün’ün 17 Temmuz 1958 tarihli Güvenlik Konseyi Başkanı’na mektupları: Lübnan ve Ürdün’ün, Birleşik Arap Cumhuriyeti’nin iç işlerine müdahalesine ilişkin şikâyetleri</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -9116,16 +8748,6 @@
           <t>kapsam_disi</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur.</t>
-        </is>
-      </c>
-      <c r="AA88" t="inlineStr">
-        <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis.</t>
-        </is>
-      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -9150,7 +8772,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lübnan'ın 22 Mayıs 1958 tarihli ve Ürdün'ün 17 Temmuz 1958 tarihli Güvenlik Konseyi Başkanı'na mektupları: Lübnan ve Ürdün'ün, Birleşik Arap Cumhuriyeti'nin iç işlerine müdahalesine ilişkin şikâyetleri</t>
+          <t>Lübnan’ın 22 Mayıs 1958 tarihli ve Ürdün’ün 17 Temmuz 1958 tarihli Güvenlik Konseyi Başkanı’na mektupları: Lübnan ve Ürdün’ün, Birleşik Arap Cumhuriyeti’nin iç işlerine müdahalesine ilişkin şikâyetleri</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -9217,16 +8839,6 @@
           <t>kapsam_disi</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur.</t>
-        </is>
-      </c>
-      <c r="AA89" t="inlineStr">
-        <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis.</t>
-        </is>
-      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -9315,12 +8927,12 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | Oy dağılımı: Aynı gün iki üyelik vetosu; ülke adına göre eşleştirildi (Tablo 4, #90).</t>
+          <t>O gün iki üyelik başvurusu veto edildi. Oy sayılarını referans tablodan ülke adına bakarak aldık (Tablo 4, #90).</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | Vote breakdown: Two membership vetoes on the same day; matched by country name (Table 4, #90).</t>
+          <t>Two membership applications were vetoed that day. We took the vote figures from the reference table by country name (Table 4, #90).</t>
         </is>
       </c>
     </row>
@@ -9411,12 +9023,12 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | Oy dağılımı: Aynı gün iki üyelik vetosu; ülke adına göre eşleştirildi (Tablo 4, #89).</t>
+          <t>O gün iki üyelik başvurusu veto edildi. Oy sayılarını referans tablodan ülke adına bakarak aldık (Tablo 4, #89).</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | Vote breakdown: Two membership vetoes on the same day; matched by country name (Table 4, #89).</t>
+          <t>Two membership applications were vetoed that day. We took the vote figures from the reference table by country name (Table 4, #89).</t>
         </is>
       </c>
     </row>
@@ -9443,7 +9055,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>SSCB'nin Genel Sekreter'e gönderdiği 13 Temmuz 1960 tarihli telgraflar</t>
+          <t>SSCB’nin Genel Sekreter’e gönderdiği 13 Temmuz 1960 tarihli telgraflar</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -9505,16 +9117,6 @@
           <t>kapsam_disi</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur.</t>
-        </is>
-      </c>
-      <c r="AA92" t="inlineStr">
-        <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis.</t>
-        </is>
-      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -9539,7 +9141,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>SSCB'nin Genel Sekreter'e gönderdiği 13 Temmuz 1960 tarihli telgraflar</t>
+          <t>SSCB’nin Genel Sekreter’e gönderdiği 13 Temmuz 1960 tarihli telgraflar</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -9601,16 +9203,6 @@
           <t>kapsam_disi</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur.</t>
-        </is>
-      </c>
-      <c r="AA93" t="inlineStr">
-        <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis.</t>
-        </is>
-      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -9635,7 +9227,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Genel Sekreter'in Güvenlik Konseyi Başkanı'na gönderdiği, Kongo'daki duruma ilişkin 13 Temmuz 1960 tarihli mektup</t>
+          <t>Genel Sekreter’in Güvenlik Konseyi Başkanı’na gönderdiği, Kongo’daki duruma ilişkin 13 Temmuz 1960 tarihli mektup</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -9697,16 +9289,6 @@
           <t>kapsam_disi</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur.</t>
-        </is>
-      </c>
-      <c r="AA94" t="inlineStr">
-        <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis.</t>
-        </is>
-      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -9805,12 +9387,12 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | scprocedure tarihi 1960-12-04. Tarih farkı 1 gün. | DHL listesindeki tarih 1960-12-03; oylama günü toplantı kaydına göre 1960-12-04. | S/PV.911: toplantı 3 Aralık 1960 Cumartesi 20.30'da başladı, 4 Aralık Pazar 03.50'de kapandı; gece yarısını geçti. Gündem tartışmasında Arjantin temsilcisi Buenos Aires'te saatin gece ikisi olduğunu söylüyor (par. 53 (PDF s. 13)); Moritanya oylaması bundan sonra, toplantının sonunda (PDF s. 46). Oylama 4 Aralık'ta, gece yarısından sonra yapıldı. Doğru tarihi referans tablo veriyor; DHL '3-4 December 1960' aralığını veriyor.</t>
+          <t>Toplantı 3 Aralık 1960 akşamı başladı, 4 Aralık sabaha karşı bitti; Moritanya oylaması toplantının sonunda, gece yarısından sonra yapıldı (S/PV.911). DHL listesi 3–4 Aralık 1960 aralığını veriyor.</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | scprocedure date 1960-12-04. Date difference 1 day. | Date in the DHL list 1960-12-03; voting day according to the meeting record 1960-12-04. | S/PV.911: the meeting opened on Saturday, 3 December 1960 at 20.30 and rose on Sunday, 4 December at 03.50; it ran past midnight. During the debate on the agenda the representative of Argentina says it is two o'clock in the morning in Buenos Aires (para. 53 (PDF p. 13)); the vote on Mauritania came after this, at the end of the meeting (PDF p. 46). The vote took place on 4 December, after midnight. The reference table gives the correct date; DHL gives the range '3-4 December 1960'.</t>
+          <t>The meeting opened on the evening of 3 December 1960 and rose in the early hours of 4 December; the vote on Mauritania came at the end, after midnight (S/PV.911). The DHL list gives the range 3–4 December 1960.</t>
         </is>
       </c>
     </row>
@@ -9837,7 +9419,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Genel Sekreter'in Güvenlik Konseyi Başkanı'na gönderdiği 13 Temmuz 1960 tarihli mektup: Kongo'daki durum</t>
+          <t>Genel Sekreter’in Güvenlik Konseyi Başkanı’na gönderdiği 13 Temmuz 1960 tarihli mektup: Kongo’daki durum</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -9899,16 +9481,6 @@
           <t>kapsam_disi</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur.</t>
-        </is>
-      </c>
-      <c r="AA96" t="inlineStr">
-        <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis.</t>
-        </is>
-      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -9938,7 +9510,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kongo Cumhuriyeti'ndeki durum</t>
+          <t>Kongo Cumhuriyeti’ndeki durum</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -10017,12 +9589,12 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | scprocedure tarihi 1961-02-20. Tarih farkı 1 gün. | Oy dağılımı 8-3-0: S/PV.942 par. 139 (PDF s. 29): S/4733/Rev.1'in birinci giriş paragrafına değişiklik önergeleri; 8 lehte, 3 aleyhte (Seylan, SSCB, Birleşik Arap Cumhuriyeti). DHL'deki iki satır birbirinin aynısı; kimlikler toplantıdaki oylama sırasına göre bağlandı. | Referans tablodaki tarih 1961-02-20; oylama günü toplantı kaydına göre 1961-02-21, DHL ile aynı. | S/PV.942: toplantı 20 Şubat 1961 Pazartesi 21.15'te başladı, 21 Şubat Salı 04.20'de kapandı; gece yarısını geçti. 00.45-01.10 ve 02.25-02.55 arasında ara verildi; birinci veto (PDF s. 29) 01.10'dan, ikinci veto (PDF s. 35) 02.55'ten sonra. Doğru tarihi DHL veriyor; referans tablo toplantının başladığı günü yazıyor.</t>
+          <t>S/4733/Rev.1’in birinci giriş paragrafına verilen değişiklik önergelerine Seylan, SSCB ve Birleşik Arap Cumhuriyeti hayır oyu verdi. DHL listesi bu iki oylamayı birbirinin aynı iki satırla gösteriyor; sıralarını toplantı kaydından aldık. | Toplantı 20 Şubat 1961 akşamı başladı, 21 Şubat sabaha karşı bitti; iki oylama da gece yarısından sonra yapıldı (S/PV.942). Referans tablo toplantının başladığı günü veriyor.</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | scprocedure date 1961-02-20. Date difference 1 day. | Vote breakdown 8-3-0: S/PV.942 para. 139 (PDF p. 29): amendments to the first preambular paragraph of S/4733/Rev.1; 8 in favour, 3 against (Ceylon, USSR, United Arab Republic). The two lines in the DHL list are identical; the identifiers were assigned in the order of the votes at the meeting. | Date in the reference table 1961-02-20; voting day according to the meeting record 1961-02-21, the same as DHL. | S/PV.942: the meeting opened on Monday, 20 February 1961 at 21.15 and rose on Tuesday, 21 February at 04.20; it ran past midnight. It was suspended from 00.45 to 01.10 and from 02.25 to 02.55; the first veto (PDF p. 29) came after 01.10, the second veto (PDF p. 35) after 02.55. DHL gives the correct date; the reference table gives the day on which the meeting opened.</t>
+          <t>Ceylon, the USSR and the United Arab Republic voted against the amendments to the first preambular paragraph of S/4733/Rev.1. The DHL list shows these two votes as identical lines; we took their order from the meeting record. | The meeting opened on the evening of 20 February 1961 and rose in the early hours of 21 February; both votes came after midnight (S/PV.942). The reference table gives the day the meeting opened.</t>
         </is>
       </c>
     </row>
@@ -10054,7 +9626,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kongo Cumhuriyeti'ndeki durum</t>
+          <t>Kongo Cumhuriyeti’ndeki durum</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -10133,12 +9705,12 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | scprocedure tarihi 1961-02-20. Tarih farkı 1 gün. | Oy dağılımı 7-3-1: S/PV.942 par. 175 (PDF s. 35): ABD'nin birinci giriş paragrafına değişiklik önergesi; 7 lehte, 3 aleyhte (Seylan, SSCB, Birleşik Arap Cumhuriyeti), 1 çekimser (Liberya). DHL'deki iki satır birbirinin aynısı; kimlikler toplantıdaki oylama sırasına göre bağlandı. | Referans tablodaki tarih 1961-02-20; oylama günü toplantı kaydına göre 1961-02-21, DHL ile aynı. | S/PV.942: toplantı 20 Şubat 1961 Pazartesi 21.15'te başladı, 21 Şubat Salı 04.20'de kapandı; gece yarısını geçti. 00.45-01.10 ve 02.25-02.55 arasında ara verildi; birinci veto (PDF s. 29) 01.10'dan, ikinci veto (PDF s. 35) 02.55'ten sonra. Doğru tarihi DHL veriyor; referans tablo toplantının başladığı günü yazıyor.</t>
+          <t>ABD’nin birinci giriş paragrafına önerdiği değişikliğe Seylan, SSCB ve Birleşik Arap Cumhuriyeti hayır oyu verdi; Liberya çekimser kaldı. DHL listesi bu iki oylamayı birbirinin aynı iki satırla gösteriyor; sıralarını toplantı kaydından aldık. | Toplantı 20 Şubat 1961 akşamı başladı, 21 Şubat sabaha karşı bitti; iki oylama da gece yarısından sonra yapıldı (S/PV.942). Referans tablo toplantının başladığı günü veriyor.</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | scprocedure date 1961-02-20. Date difference 1 day. | Vote breakdown 7-3-1: S/PV.942 para. 175 (PDF p. 35): United States amendment to the first preambular paragraph; 7 in favour, 3 against (Ceylon, USSR, United Arab Republic), 1 abstaining (Liberia). The two lines in the DHL list are identical; the identifiers were assigned in the order of the votes at the meeting. | Date in the reference table 1961-02-20; voting day according to the meeting record 1961-02-21, the same as DHL. | S/PV.942: the meeting opened on Monday, 20 February 1961 at 21.15 and rose on Tuesday, 21 February at 04.20; it ran past midnight. It was suspended from 00.45 to 01.10 and from 02.25 to 02.55; the first veto (PDF p. 29) came after 01.10, the second veto (PDF p. 35) after 02.55. DHL gives the correct date; the reference table gives the day on which the meeting opened.</t>
+          <t>Ceylon, the USSR and the United Arab Republic voted against the United States amendment to the first preambular paragraph; Liberia abstained. The DHL list shows these two votes as identical lines; we took their order from the meeting record. | The meeting opened on the evening of 20 February 1961 and rose in the early hours of 21 February; both votes came after midnight (S/PV.942). The reference table gives the day the meeting opened.</t>
         </is>
       </c>
     </row>
@@ -10165,7 +9737,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kuveyt'in, Irak'ın Kuveyt'in toprak bütünlüğüne yönelik tehdidinden doğan duruma ilişkin şikâyetleri</t>
+          <t>Kuveyt’in, Irak’ın Kuveyt’in toprak bütünlüğüne yönelik tehdidinden doğan duruma ilişkin şikâyetleri</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -10227,16 +9799,6 @@
           <t>kapsam_disi</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur.</t>
-        </is>
-      </c>
-      <c r="AA99" t="inlineStr">
-        <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis.</t>
-        </is>
-      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -10261,7 +9823,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kongo Cumhuriyeti'ndeki durum</t>
+          <t>Kongo Cumhuriyeti’ndeki durum</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -10340,12 +9902,12 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | Oy dağılımı 9-1-1: S/PV.982 par. 81 (PDF s. 18): ABD'nin S/4985/Rev.1'e üçüncü değişiklik önergesi (2. karar paragrafının değiştirilmesi); 9 lehte, 1 aleyhte (SSCB), 1 çekimser (Fransa). Kayıt taranmış görüntü, metin katmanı yok; sayfa görüntüsünden okundu. DHL'deki iki satır birbirinin aynısı; kimlikler toplantıdaki oylama sırasına göre bağlandı.</t>
+          <t>ABD’nin S/4985/Rev.1’e verdiği üçüncü değişiklik önergesi 2. karar paragrafını değiştiriyordu. SSCB hayır oyu verdi; Fransa çekimser kaldı. DHL listesi bu iki oylamayı birbirinin aynı iki satırla gösteriyor; sıralarını toplantı kaydından aldık.</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | Vote breakdown 9-1-1: S/PV.982 para. 81 (PDF p. 18): third United States amendment to S/4985/Rev.1 (amending operative paragraph 2); 9 in favour, 1 against (USSR), 1 abstaining (France). The record is a scanned image without a text layer; read from the page image. The two lines in the DHL list are identical; the identifiers were assigned in the order of the votes at the meeting.</t>
+          <t>The third United States amendment to S/4985/Rev.1 would have amended operative paragraph 2. The USSR voted against; France abstained. The DHL list shows these two votes as identical lines; we took their order from the meeting record.</t>
         </is>
       </c>
     </row>
@@ -10372,7 +9934,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kongo Cumhuriyeti'ndeki durum</t>
+          <t>Kongo Cumhuriyeti’ndeki durum</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -10451,12 +10013,12 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | Oy dağılımı 9-1-1: S/PV.982 par. 84 (PDF s. 19): ABD'nin altıncı değişiklik önergesi (yeni 11. paragraf); 9 lehte, 1 aleyhte (SSCB), 1 çekimser (Fransa). Beşinci önerge veto ile değil, yedi olumlu oy alamadığı için düştü (6-1-3). DHL'deki iki satır birbirinin aynısı; kimlikler toplantıdaki oylama sırasına göre bağlandı.</t>
+          <t>ABD’nin altıncı değişiklik önergesi yeni bir 11. paragraf ekliyordu. SSCB hayır oyu verdi; Fransa çekimser kaldı. Beşinci önerge veto ile değil, yedi olumlu oy alamadığı için düştü (6-1-3). DHL listesi bu iki oylamayı birbirinin aynı iki satırla gösteriyor; sıralarını toplantı kaydından aldık.</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | Vote breakdown 9-1-1: S/PV.982 para. 84 (PDF p. 19): sixth United States amendment (new paragraph 11); 9 in favour, 1 against (USSR), 1 abstaining (France). The fifth amendment failed not because of a veto but because it did not obtain seven affirmative votes (6-1-3). The two lines in the DHL list are identical; the identifiers were assigned in the order of the votes at the meeting.</t>
+          <t>The sixth United States amendment would have added a new paragraph 11. The USSR voted against; France abstained. The fifth amendment failed not because of a veto but because it did not obtain seven affirmative votes (6-1-3). The DHL list shows these two votes as identical lines; we took their order from the meeting record.</t>
         </is>
       </c>
     </row>
@@ -10545,16 +10107,6 @@
           <t>kapsam_disi</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur.</t>
-        </is>
-      </c>
-      <c r="AA102" t="inlineStr">
-        <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis.</t>
-        </is>
-      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -10579,7 +10131,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Portekiz'in Güvenlik Konseyi Başkanı'na gönderdiği, Goa'ya ilişkin 18 Aralık 1961 tarihli mektup</t>
+          <t>Portekiz’in Güvenlik Konseyi Başkanı’na gönderdiği, Goa’ya ilişkin 18 Aralık 1961 tarihli mektup</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -10641,16 +10193,6 @@
           <t>kapsam_disi</t>
         </is>
       </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur.</t>
-        </is>
-      </c>
-      <c r="AA103" t="inlineStr">
-        <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis.</t>
-        </is>
-      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -10737,16 +10279,6 @@
           <t>kapsam_disi</t>
         </is>
       </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur.</t>
-        </is>
-      </c>
-      <c r="AA104" t="inlineStr">
-        <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis.</t>
-        </is>
-      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -10833,16 +10365,6 @@
           <t>kapsam_disi</t>
         </is>
       </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur.</t>
-        </is>
-      </c>
-      <c r="AA105" t="inlineStr">
-        <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis.</t>
-        </is>
-      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -10867,7 +10389,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Güney Rodezya'daki durum</t>
+          <t>Güney Rodezya’daki durum</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -10953,7 +10475,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Malezya'nın Güvenlik Konseyi Başkanı'na gönderdiği 3 Eylül 1964 tarihli mektup</t>
+          <t>Malezya’nın Güvenlik Konseyi Başkanı’na gönderdiği 3 Eylül 1964 tarihli mektup</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -11015,16 +10537,6 @@
           <t>kapsam_disi</t>
         </is>
       </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur.</t>
-        </is>
-      </c>
-      <c r="AA107" t="inlineStr">
-        <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis.</t>
-        </is>
-      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -11111,16 +10623,6 @@
           <t>kapsam_disi</t>
         </is>
       </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur.</t>
-        </is>
-      </c>
-      <c r="AA108" t="inlineStr">
-        <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis.</t>
-        </is>
-      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -11207,16 +10709,6 @@
           <t>kapsam_disi</t>
         </is>
       </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur.</t>
-        </is>
-      </c>
-      <c r="AA109" t="inlineStr">
-        <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis.</t>
-        </is>
-      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -11246,7 +10738,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kanada, Danimarka, Fransa, Paraguay, Birleşik Krallık ve ABD'nin Güvenlik Konseyi Başkanı'na gönderdiği, Çekoslovakya'daki duruma ilişkin 21 Ağustos 1968 tarihli mektup</t>
+          <t>Kanada, Danimarka, Fransa, Paraguay, Birleşik Krallık ve ABD’nin Güvenlik Konseyi Başkanı’na gönderdiği, Çekoslovakya’daki duruma ilişkin 21 Ağustos 1968 tarihli mektup</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -11315,12 +10807,12 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | scprocedure tarihi 1968-08-23. Tarih farkı 1 gün. | DHL listesindeki tarih 1968-08-22; oylama günü toplantı kaydına göre 1968-08-23. | S/PV.1443: toplantı 22 Ağustos 1968 Perşembe 21.00 için çağrıldı, 22.00'ye ertelendi (par. 53), 23 Ağustos Cuma 03.55'te kapandı; gece yarısını geçti. Oylamadan önce konuşmacılar 22 Ağustos sabahki toplantıdan 'dün sabah' diye söz ediyor (par. 255 (PDF s. 28-29) ve 257); oylama PDF s. 31; Başkan oylamadan sonra toplantıyı 'bugün, 23 Ağustos Cuma' 17.00'ye erteliyor (PDF s. 33). Doğru tarihi referans tablo veriyor; DHL toplantının başladığı günü yazıyor.</t>
+          <t>Toplantı 22 Ağustos 1968 akşamı başladı, oylama gece yarısından sonra, 23 Ağustos’ta yapıldı (S/PV.1443). DHL listesi toplantının başladığı günü veriyor.</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | scprocedure date 1968-08-23. Date difference 1 day. | Date in the DHL list 1968-08-22; voting day according to the meeting record 1968-08-23. | S/PV.1443: the meeting was convened for Thursday, 22 August 1968 at 21.00, was postponed to 22.00 (para. 53) and rose on Friday, 23 August at 03.55; it ran past midnight. Before the vote, speakers refer to the meeting of the morning of 22 August as the previous morning (PDF pp. 28-29, paras. 255 and 257); vote PDF p. 31; after the vote the President adjourns the meeting until 17.00 the same day, Friday, 23 August (PDF p. 33). The reference table gives the correct date; DHL gives the day on which the meeting opened.</t>
+          <t>The meeting opened on the evening of 22 August 1968 and the vote came after midnight, on 23 August (S/PV.1443). The DHL list gives the day the meeting opened.</t>
         </is>
       </c>
     </row>
@@ -11347,7 +10839,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Güney Rodezya'daki duruma ilişkin mesele</t>
+          <t>Güney Rodezya’daki duruma ilişkin mesele</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -11433,7 +10925,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Güney Rodezya'daki duruma ilişkin mesele</t>
+          <t>Güney Rodezya’daki duruma ilişkin mesele</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -11519,7 +11011,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Arjantin, Belçika, Burundi, İtalya, Japonya, Nikaragua, Somali, Birleşik Krallık ve ABD'nin Güvenlik Konseyi Başkanı'na gönderdiği, Hindistan-Pakistan meselesine ilişkin 4 Aralık 1971 tarihli mektup</t>
+          <t>Arjantin, Belçika, Burundi, İtalya, Japonya, Nikaragua, Somali, Birleşik Krallık ve ABD’nin Güvenlik Konseyi Başkanı’na gönderdiği, Hindistan-Pakistan meselesine ilişkin 4 Aralık 1971 tarihli mektup</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -11581,16 +11073,6 @@
           <t>kapsam_disi</t>
         </is>
       </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur.</t>
-        </is>
-      </c>
-      <c r="AA113" t="inlineStr">
-        <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis.</t>
-        </is>
-      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -11615,7 +11097,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Arjantin, Belçika, Burundi, İtalya, Japonya, Nikaragua, Somali, Birleşik Krallık ve ABD'nin Güvenlik Konseyi Başkanı'na gönderdiği, Hindistan-Pakistan meselesine ilişkin 4 Aralık 1971 tarihli mektup</t>
+          <t>Arjantin, Belçika, Burundi, İtalya, Japonya, Nikaragua, Somali, Birleşik Krallık ve ABD’nin Güvenlik Konseyi Başkanı’na gönderdiği, Hindistan-Pakistan meselesine ilişkin 4 Aralık 1971 tarihli mektup</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -11677,16 +11159,6 @@
           <t>kapsam_disi</t>
         </is>
       </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur.</t>
-        </is>
-      </c>
-      <c r="AA114" t="inlineStr">
-        <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis.</t>
-        </is>
-      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -11711,7 +11183,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>ABD'nin Güvenlik Konseyi Başkanı'na gönderdiği, Hindistan-Pakistan meselesine ilişkin 12 Aralık 1971 tarihli mektup</t>
+          <t>ABD’nin Güvenlik Konseyi Başkanı’na gönderdiği, Hindistan-Pakistan meselesine ilişkin 12 Aralık 1971 tarihli mektup</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -11773,16 +11245,6 @@
           <t>kapsam_disi</t>
         </is>
       </c>
-      <c r="Z115" t="inlineStr">
-        <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur.</t>
-        </is>
-      </c>
-      <c r="AA115" t="inlineStr">
-        <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis.</t>
-        </is>
-      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -11807,7 +11269,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Güney Rodezya'daki duruma ilişkin mesele</t>
+          <t>Güney Rodezya’daki duruma ilişkin mesele</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -11893,7 +11355,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Güvenlik Konseyi'nin hâlen ele aldığı Afrika'ya ilişkin meselelerin görüşülmesi ve Konsey'in ilgili kararlarının uygulanması: Güney Rodezya'daki durum</t>
+          <t>Güvenlik Konseyinin hâlen ele aldığı Afrika’ya ilişkin meselelerin görüşülmesi ve Konseyin ilgili kararlarının uygulanması: Güney Rodezya’daki durum</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -12065,7 +11527,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Ortadoğu'daki durum</t>
+          <t>Ortadoğu’daki durum</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -12151,7 +11613,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Ortadoğu'ya ilişkin karar taslağına değişiklik önergesi</t>
+          <t>Ortadoğu’ya ilişkin karar taslağına değişiklik önergesi</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -12230,12 +11692,12 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>DHL listesi aynı gündeki yalnızca ABD vetosunu içeriyor. S/PV.1662 par. 72 (PDF s. 8, basılı s. 6): Belçika, Fransa, İtalya ve Birleşik Krallık'ın S/10784 taslağına önerdiği değişikliklerin (S/10786) 2 (a) paragrafı ayrı oylandı. Bu paragraf, taslağın karar paragrafındaki "the parties" ifadesini "all parties" ile değiştiriyordu (par. 7 (PDF s. 3); par. 63 (PDF s. 8)). 9 lehte, 6 aleyhte (Çin, Gine, Somali, Sudan, SSCB, Yugoslavya), çekimser yok. Kayıt: "Paragraph 2, subparagraph (a) was not adopted, two of the negative votes being those of permanent members." Bu oylama, aynı toplantıda S/10784'ün ABD vetosuyla düştüğü oylamadan önce yapıldı (par. 74 (PDF s. 9); 13-1-1); scprocedure Tablo 4 ise ABD vetosunu önce (#118), bu vetoyu sonra (#119) veriyor. Değişikliklerin 1. paragrafı (8-4-3) ve 2 (b) paragrafı (8-7-0) dokuz olumlu oy alamadığı için kabul edilmedi; bunlar veto değildir (PDF s. 8-9). Toplantı 10 Eylül 1972 Pazar öğleden sonra 5.40'ta açıldı, akşam 8.45'te bitti (PDF s. 3 ve 21). Sayfa numaraları PDF sayfasıdır (basılı sayfa = PDF sayfası - 2).</t>
+          <t>DHL listesi bu günden yalnızca ABD vetosunu veriyor. Belçika, Fransa, İtalya ve Birleşik Krallık’ın S/10784’e önerdiği değişikliklerin (S/10786) 2 (a) paragrafı ayrıca oylandı; bu paragraf karar paragrafındaki “the parties” ifadesini “all parties” yapıyordu (par. 7 ve 63). Paragraf Çin ve SSCB’nin ret oyu nedeniyle kabul edilmedi; Gine, Somali, Sudan ve Yugoslavya da hayır oyu verdi (S/PV.1662, par. 72). Bu oylama, S/10784’ün ABD vetosuyla düştüğü oylamadan önce yapıldı (par. 74); referans tablo ise ABD vetosunu önce, bu vetoyu sonra veriyor (Tablo 4, #118 ve #119). Değişikliklerin 1. paragrafı (8-4-3) ve 2 (b) paragrafı (8-7-0) dokuz olumlu oy alamadığı için kabul edilmedi; bunlar veto değildir.</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>The DHL list includes only the US veto of the same day. S/PV.1662 para. 72 (PDF p. 8, printed p. 6): paragraph 2 (a) of the amendments of Belgium, France, Italy and the United Kingdom to draft S/10784 (S/10786) was put to a separate vote. This paragraph replaced the words "the parties" by "all parties" in the operative paragraph of the draft (para. 7 (PDF p. 3); para. 63 (PDF p. 8)). 9 in favour, 6 against (China, Guinea, Somalia, Sudan, USSR, Yugoslavia), no abstentions. The record: "Paragraph 2, subparagraph (a) was not adopted, two of the negative votes being those of permanent members." This vote was taken before the vote in which S/10784 failed because of the US veto at the same meeting (para. 74 (PDF p. 9); 13-1-1); scprocedure Table 4 lists the US veto first (No. 118) and this veto second (No. 119). Paragraph 1 of the amendments (8-4-3) and paragraph 2 (b) (8-7-0) were not adopted, having failed to obtain nine affirmative votes; these are not vetoes (PDF pp. 8-9). The meeting was called to order on Sunday, 10 September 1972 at 5.40 p.m. and rose at 8.45 p.m. (PDF pp. 3 and 21). Page numbers are PDF pages (printed page = PDF page - 2).</t>
+          <t>The DHL list gives only the US veto for this day. Paragraph 2 (a) of the amendments of Belgium, France, Italy and the United Kingdom to S/10784 (S/10786) was put to a separate vote; it replaced “the parties” with “all parties” in the operative paragraph (paras. 7 and 63). The paragraph was not adopted because of the negative votes of China and the USSR; Guinea, Somalia, Sudan and Yugoslavia also voted against (S/PV.1662, para. 72). This vote was taken before the vote in which S/10784 failed because of the US veto (para. 74); the reference table lists the US veto first and this veto second (Table 4, #118 and #119). Paragraph 1 of the amendments (8-4-3) and paragraph 2 (b) (8-7-0) were not adopted because they did not obtain nine affirmative votes; these are not vetoes.</t>
         </is>
       </c>
     </row>
@@ -12262,7 +11724,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Güney Rodezya'daki duruma ilişkin mesele</t>
+          <t>Güney Rodezya’daki duruma ilişkin mesele</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -12348,7 +11810,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Latin Amerika'da barış ve güvenliğin korunması ve güçlendirilmesine yönelik önlemlerin görüşülmesi</t>
+          <t>Latin Amerika’da barış ve güvenliğin korunması ve güçlendirilmesine yönelik önlemlerin görüşülmesi</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -12434,7 +11896,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Güney Rodezya'daki duruma ilişkin mesele</t>
+          <t>Güney Rodezya’daki duruma ilişkin mesele</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -12520,7 +11982,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Ortadoğu'daki durum</t>
+          <t>Ortadoğu’daki durum</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -12606,7 +12068,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kıbrıs'taki durum</t>
+          <t>Kıbrıs’taki durum</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -12668,16 +12130,6 @@
           <t>kapsam_disi</t>
         </is>
       </c>
-      <c r="Z125" t="inlineStr">
-        <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur.</t>
-        </is>
-      </c>
-      <c r="AA125" t="inlineStr">
-        <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis.</t>
-        </is>
-      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -12788,7 +12240,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Namibya'daki durum</t>
+          <t>Namibya’daki durum</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -13218,7 +12670,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Ortadoğu'daki durum</t>
+          <t>Ortadoğu’daki durum</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -13304,7 +12756,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Filistin meselesi dahil Ortadoğu sorunu</t>
+          <t>Filistin meselesi dâhil Ortadoğu’daki durum</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -13390,7 +12842,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Komorlar'daki durum</t>
+          <t>Komorlar’daki durum</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -13476,7 +12928,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Libya ve Pakistan'ın, işgal altındaki Arap topraklarındaki son gelişmelerden doğan ciddi durumun görüşülmesi talebi</t>
+          <t>Libya ve Pakistan’ın, işgal altındaki Arap topraklarındaki son gelişmelerden doğan ciddi durumun görüşülmesi talebi</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -13734,7 +13186,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Namibya'daki durum</t>
+          <t>Namibya’daki durum</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -14164,7 +13616,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Demokratik Kampuçya'nın Güvenlik Konseyi Başkanı'na gönderdiği 3 Ocak 1979 tarihli telgraf</t>
+          <t>Demokratik Kampuçya’nın Güvenlik Konseyi Başkanı’na gönderdiği 3 Ocak 1979 tarihli telgraf</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -14226,16 +13678,6 @@
           <t>kapsam_disi</t>
         </is>
       </c>
-      <c r="Z143" t="inlineStr">
-        <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur.</t>
-        </is>
-      </c>
-      <c r="AA143" t="inlineStr">
-        <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis.</t>
-        </is>
-      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -14260,7 +13702,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Güneydoğu Asya'daki durum ve bunun uluslararası barış ve güvenlik açısından sonuçları: Çin-Vietnam sınır anlaşmazlığı</t>
+          <t>Güneydoğu Asya’daki durum ve bunun uluslararası barış ve güvenlik açısından sonuçları: Çin-Vietnam sınır anlaşmazlığı</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -14322,16 +13764,6 @@
           <t>kapsam_disi</t>
         </is>
       </c>
-      <c r="Z144" t="inlineStr">
-        <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur.</t>
-        </is>
-      </c>
-      <c r="AA144" t="inlineStr">
-        <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis.</t>
-        </is>
-      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -14356,7 +13788,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>52 ülkenin Güvenlik Konseyi Başkanı'na gönderdiği 3 Ocak 1980 tarihli mektup</t>
+          <t>52 ülkenin Güvenlik Konseyi Başkanı’na gönderdiği 3 Ocak 1980 tarihli mektup</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -14420,12 +13852,12 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | Kaynakta tarih aralığı var; oylama günü toplantı kaydından doğrulanmalı.</t>
+          <t>DHL listesi bu oylamanın tarihini bir aralık olarak veriyor.</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | The source gives a date range; the voting day is to be verified from the meeting record.</t>
+          <t>The DHL list gives the date of this vote as a range.</t>
         </is>
       </c>
     </row>
@@ -14457,7 +13889,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>ABD'nin Güvenlik Konseyi Başkanı'na gönderdiği 22 Aralık 1979 tarihli mektuplar: ABD ve İran rehine meselesi</t>
+          <t>ABD’nin Güvenlik Konseyi Başkanı’na gönderdiği 22 Aralık 1979 tarihli mektuplar: ABD ve İran rehine meselesi</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -14536,12 +13968,12 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur. | scprocedure tarihi 1980-01-13. Tarih farkı 2 gün. | DHL listesindeki tarih 1980-01-11; oylama günü toplantı kaydına göre 1980-01-13. | S/PV.2191 and Add.1 (BM Dijital Kütüphanesi'nden elle indirildi: kaynaklar/.belgeler/S_PV.2191_Add.1.pdf): toplantı iki oturumda yapıldı. Başlık: 'Held in New York on Friday, 11 January 1980, at 9 p.m. and on Sunday, 13 January 1980, at 8 p.m.' (PDF s. 3). Birinci oturum 11 Ocak Cuma 21.15'te açıldı; ABD'nin önerisiyle oylama yapılmadan 21.20'de ara verildi, 13 Ocak Pazar 20.40'ta yeniden açıldı (par. 9, PDF s. 4). S/13735 ikinci oturumda oylandı (par. 149 (PDF s. 16)); toplantı 13 Ocak 22.45'te kapandı (PDF s. 18). Gece yarısı geçilmedi; oylama günü 13 Ocak 1980. Doğru tarihi referans tablo veriyor; DHL toplantının iki gününü aralık olarak veriyor. Sayfa numaraları bu PDF dosyasının sayfalarıdır. | Oy dağılımı 10-2-2: S/PV.2191 par. 149 (PDF s. 16): S/13735 (ABD taslağı); 10 lehte, 2 aleyhte (Alman Demokratik Cumhuriyeti, SSCB), 2 çekimser (Bangladeş, Meksika); Çin oylamaya katılmadı. Kayıtta 'ret oylarından biri bir daimi üyeye ait' deniyor.</t>
+          <t>Toplantı iki oturumda yapıldı. 11 Ocak 1980 Cuma akşamı açılan birinci oturuma oylama yapılmadan ara verildi; S/13735 ise 13 Ocak Pazar akşamı oylandı (S/PV.2191, par. 149). DHL listesi 11–13 Ocak 1980 aralığını veriyor. | ABD taslağına (S/13735) Alman Demokratik Cumhuriyeti ve SSCB hayır oyu verdi; Bangladeş ve Meksika çekimser kaldı. Çin oylamaya katılmadı. Kayıtta “ret oylarından biri bir daimî üyeye ait” deniyor.</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis. | scprocedure date 1980-01-13. Date difference 2 days. | Date in the DHL list 1980-01-11; voting day according to the meeting record 1980-01-13. | S/PV.2191 and Add.1 (downloaded manually from the UN Digital Library: kaynaklar/.belgeler/S_PV.2191_Add.1.pdf): the meeting was held in two parts. Heading: 'Held in New York on Friday, 11 January 1980, at 9 p.m. and on Sunday, 13 January 1980, at 8 p.m.' (PDF p. 3). The first part opened on Friday, 11 January at 21.15; at the proposal of the United States it was suspended at 21.20 without a vote, and resumed on Sunday, 13 January at 20.40 (para. 9, PDF p. 4). S/13735 was voted on in the second part (para. 149 (PDF p. 16)); the meeting rose on 13 January at 22.45 (PDF p. 18). Midnight was not passed; the voting day is 13 January 1980. The reference table gives the correct date; DHL gives the two days of the meeting as a range. Page numbers are the pages of this PDF file. | Vote breakdown 10-2-2: S/PV.2191 para. 149 (PDF p. 16): S/13735 (United States draft); 10 in favour, 2 against (German Democratic Republic, USSR), 2 abstaining (Bangladesh, Mexico); China did not participate in the vote. The record says 'one of the negatives votes being that of a permanent member of the Council' [sic].</t>
+          <t>The meeting was held in two parts. The first opened on the evening of Friday 11 January 1980 and was suspended without a vote; S/13735 was put to the vote on the evening of Sunday 13 January (S/PV.2191, para. 149). The DHL list gives the range 11–13 January 1980. | The German Democratic Republic and the USSR voted against the United States draft (S/13735); Bangladesh and Mexico abstained. China did not participate in the vote. The record says “one of the negatives votes being that of a permanent member of the Council” [sic].</t>
         </is>
       </c>
     </row>
@@ -14654,7 +14086,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Namibya'daki durum</t>
+          <t>Namibya’daki durum</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -14733,12 +14165,12 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>Oy dağılımı 12-3-0: S/PV.2277 PDF s. 5: S/14462; 12 lehte, 3 aleyhte (Fransa, Birleşik Krallık, ABD).</t>
+          <t>Fransa, Birleşik Krallık ve ABD hayır oyu verdi; çekimser kalan olmadı.</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>Vote breakdown 12-3-0: S/PV.2277 PDF p. 5: S/14462; 12 in favour, 3 against (France, United Kingdom, United States).</t>
+          <t>France, the United Kingdom and the United States voted against; there were no abstentions.</t>
         </is>
       </c>
     </row>
@@ -14765,7 +14197,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Namibya'daki durum</t>
+          <t>Namibya’daki durum</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -14844,12 +14276,12 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>Oy dağılımı 11-3-1: S/PV.2277 PDF s. 5: S/14461; 11 lehte, 3 aleyhte (Fransa, Birleşik Krallık, ABD), 1 çekimser (Japonya).</t>
+          <t>Fransa, Birleşik Krallık ve ABD hayır oyu verdi; Japonya çekimser kaldı.</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>Vote breakdown 11-3-1: S/PV.2277 PDF p. 5: S/14461; 11 in favour, 3 against (France, United Kingdom, United States), 1 abstaining (Japan).</t>
+          <t>France, the United Kingdom and the United States voted against; Japan abstained.</t>
         </is>
       </c>
     </row>
@@ -14876,7 +14308,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Namibya'daki durum</t>
+          <t>Namibya’daki durum</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -14955,12 +14387,12 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>Oy dağılımı 9-3-3: S/PV.2277 PDF s. 5: S/14460/Rev.1; 9 lehte, 3 aleyhte (Fransa, Birleşik Krallık, ABD), 3 çekimser (İrlanda, Japonya, İspanya).</t>
+          <t>Fransa, Birleşik Krallık ve ABD hayır oyu verdi; İrlanda, Japonya ve İspanya çekimser kaldı.</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>Vote breakdown 9-3-3: S/PV.2277 PDF p. 5: S/14460/Rev.1; 9 in favour, 3 against (France, United Kingdom, United States), 3 abstaining (Ireland, Japan, Spain).</t>
+          <t>France, the United Kingdom and the United States voted against; Ireland, Japan and Spain abstained.</t>
         </is>
       </c>
     </row>
@@ -14987,7 +14419,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Namibya'daki durum</t>
+          <t>Namibya’daki durum</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -15066,12 +14498,12 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>Oy dağılımı 9-3-3: S/PV.2277 PDF s. 5: S/14459; 9 lehte, 3 aleyhte (Fransa, Birleşik Krallık, ABD), 3 çekimser (İrlanda, Japonya, İspanya).</t>
+          <t>Fransa, Birleşik Krallık ve ABD hayır oyu verdi; İrlanda, Japonya ve İspanya çekimser kaldı.</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>Vote breakdown 9-3-3: S/PV.2277 PDF p. 5: S/14459; 9 in favour, 3 against (France, United Kingdom, United States), 3 abstaining (Ireland, Japan, Spain).</t>
+          <t>France, the United Kingdom and the United States voted against; Ireland, Japan and Spain abstained.</t>
         </is>
       </c>
     </row>
@@ -15098,7 +14530,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Angola'nın Güney Afrika'ya karşı şikâyeti</t>
+          <t>Angola’nın Güney Afrika’ya karşı şikâyeti</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -15334,12 +14766,12 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>Oy dağılımı: Aynı gün iki farklı gündem; konuya göre eşleştirildi (Tablo 4, #154).</t>
+          <t>O gün iki ayrı gündem maddesinde veto kullanıldı. Oy sayılarını referans tablodan konuya bakarak aldık (Tablo 4, #154).</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>Vote breakdown: Two different agenda items on the same day; matched by subject (Table 4, #154).</t>
+          <t>Vetoes were cast on two different agenda items that day. We took the vote figures from the reference table by subject (Table 4, #154).</t>
         </is>
       </c>
     </row>
@@ -15366,7 +14798,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Nikaragua'nın Genel Sekreter'e gönderdiği 19 Mart 1982 tarihli mektup</t>
+          <t>Nikaragua’nın Genel Sekreter’e gönderdiği 19 Mart 1982 tarihli mektup</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -15430,12 +14862,12 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>Oy dağılımı: Aynı gün iki farklı gündem; konuya göre eşleştirildi (Tablo 4, #153).</t>
+          <t>O gün iki ayrı gündem maddesinde veto kullanıldı. Oy sayılarını referans tablodan konuya bakarak aldık (Tablo 4, #153).</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>Vote breakdown: Two different agenda items on the same day; matched by subject (Table 4, #153).</t>
+          <t>Vetoes were cast on two different agenda items that day. We took the vote figures from the reference table by subject (Table 4, #153).</t>
         </is>
       </c>
     </row>
@@ -15634,7 +15066,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Ortadoğu'daki durum</t>
+          <t>Ortadoğu’daki durum</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -15720,7 +15152,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Ortadoğu'daki durum</t>
+          <t>Ortadoğu’daki durum</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -15806,7 +15238,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Ortadoğu'daki durum</t>
+          <t>Ortadoğu’daki durum</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -15978,7 +15410,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>ABD, Kore Cumhuriyeti, Kanada ve Japonya'nın Güvenlik Konseyi Başkanı'na gönderdiği 1 Eylül 1983 tarihli mektuplar ve Avustralya'nın Güvenlik Konseyi Başkanı'na gönderdiği 2 Eylül 1983 tarihli mektup</t>
+          <t>ABD, Kore Cumhuriyeti, Kanada ve Japonya’nın Güvenlik Konseyi Başkanı’na gönderdiği 1 Eylül 1983 tarihli mektuplar ve Avustralya’nın Güvenlik Konseyi Başkanı’na gönderdiği 2 Eylül 1983 tarihli mektup</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -16040,16 +15472,6 @@
           <t>kapsam_disi</t>
         </is>
       </c>
-      <c r="Z162" t="inlineStr">
-        <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur.</t>
-        </is>
-      </c>
-      <c r="AA162" t="inlineStr">
-        <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis.</t>
-        </is>
-      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -16074,7 +15496,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Grenada'daki durum</t>
+          <t>Grenada’daki durum</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -16138,12 +15560,12 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>Kaynakta tarih aralığı var; oylama günü toplantı kaydından doğrulanmalı.</t>
+          <t>DHL listesi bu oylamanın tarihini bir aralık olarak veriyor.</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>The source gives a date range; the voting day is to be verified from the meeting record.</t>
+          <t>The DHL list gives the date of this vote as a range.</t>
         </is>
       </c>
     </row>
@@ -16170,7 +15592,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Ortadoğu'daki durum</t>
+          <t>Ortadoğu’daki durum</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -16232,16 +15654,6 @@
           <t>kapsam_disi</t>
         </is>
       </c>
-      <c r="Z164" t="inlineStr">
-        <is>
-          <t>SSCB vetosu; Rusya Federasyonu koltuğun halefidir, analizde ayrı tutulur.</t>
-        </is>
-      </c>
-      <c r="AA164" t="inlineStr">
-        <is>
-          <t>USSR veto; the Russian Federation is the successor to the seat and is kept separate in the analysis.</t>
-        </is>
-      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -16266,7 +15678,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Nikaragua'nın Güvenlik Konseyi Başkanı'na gönderdiği 29 Mart 1984 tarihli mektup</t>
+          <t>Nikaragua’nın Güvenlik Konseyi Başkanı’na gönderdiği 29 Mart 1984 tarihli mektup</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -16352,7 +15764,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Ortadoğu'daki durum</t>
+          <t>Ortadoğu’daki durum</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -16438,7 +15850,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Ortadoğu'daki durum</t>
+          <t>Ortadoğu’daki durum</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -16524,7 +15936,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Nikaragua'nın Güvenlik Konseyi Başkanı'na gönderdiği 6 Mayıs 1985 tarihli mektup</t>
+          <t>Nikaragua’nın Güvenlik Konseyi Başkanı’na gönderdiği 6 Mayıs 1985 tarihli mektup</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -16603,12 +16015,12 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>Oy dağılımı 13-1-1: S/PV.2580 par. 266 (PDF s. 29): S/17172'nin sekizinci giriş paragrafı (ayrı oylama); 13 lehte, 1 aleyhte (ABD), 1 çekimser (Birleşik Krallık). DHL'deki üç satır birbirinin aynısı; kimlikler toplantıdaki oylama sırasına göre bağlandı.</t>
+          <t>S/17172’nin sekizinci giriş paragrafı ayrıca oylandı. ABD hayır oyu verdi; Birleşik Krallık çekimser kaldı. DHL listesi bu üç oylamayı birbirinin aynı üç satırla gösteriyor; sıralarını toplantı kaydından aldık.</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>Vote breakdown 13-1-1: S/PV.2580 para. 266 (PDF p. 29): eighth preambular paragraph of S/17172 (separate vote); 13 in favour, 1 against (United States), 1 abstaining (United Kingdom). The three lines in the DHL list are identical; the identifiers were assigned in the order of the votes at the meeting.</t>
+          <t>The eighth preambular paragraph of S/17172 was put to a separate vote. The United States voted against; the United Kingdom abstained. The DHL list shows these three votes as identical lines; we took their order from the meeting record.</t>
         </is>
       </c>
     </row>
@@ -16635,7 +16047,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Nikaragua'nın Güvenlik Konseyi Başkanı'na gönderdiği 6 Mayıs 1985 tarihli mektup</t>
+          <t>Nikaragua’nın Güvenlik Konseyi Başkanı’na gönderdiği 6 Mayıs 1985 tarihli mektup</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -16714,12 +16126,12 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>Oy dağılımı 11-1-3: S/PV.2580 par. 267 (PDF s. 29): S/17172'nin birinci karar paragrafı (ayrı oylama); 11 lehte, 1 aleyhte (ABD), 3 çekimser (Mısır, Tayland, Birleşik Krallık). DHL'deki üç satır birbirinin aynısı; kimlikler toplantıdaki oylama sırasına göre bağlandı.</t>
+          <t>S/17172’nin birinci karar paragrafı ayrıca oylandı. ABD hayır oyu verdi; Mısır, Tayland ve Birleşik Krallık çekimser kaldı. DHL listesi bu üç oylamayı birbirinin aynı üç satırla gösteriyor; sıralarını toplantı kaydından aldık.</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>Vote breakdown 11-1-3: S/PV.2580 para. 267 (PDF p. 29): first operative paragraph of S/17172 (separate vote); 11 in favour, 1 against (United States), 3 abstaining (Egypt, Thailand, United Kingdom). The three lines in the DHL list are identical; the identifiers were assigned in the order of the votes at the meeting.</t>
+          <t>The first operative paragraph of S/17172 was put to a separate vote. The United States voted against; Egypt, Thailand and the United Kingdom abstained. The DHL list shows these three votes as identical lines; we took their order from the meeting record.</t>
         </is>
       </c>
     </row>
@@ -16746,7 +16158,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Nikaragua'nın Güvenlik Konseyi Başkanı'na gönderdiği 6 Mayıs 1985 tarihli mektup</t>
+          <t>Nikaragua’nın Güvenlik Konseyi Başkanı’na gönderdiği 6 Mayıs 1985 tarihli mektup</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -16825,12 +16237,12 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>Oy dağılımı 13-1-1: S/PV.2580 par. 268 (PDF s. 30): S/17172'nin ikinci karar paragrafı (ayrı oylama); 13 lehte, 1 aleyhte (ABD), 1 çekimser (Birleşik Krallık). DHL'deki üç satır birbirinin aynısı; kimlikler toplantıdaki oylama sırasına göre bağlandı.</t>
+          <t>S/17172’nin ikinci karar paragrafı ayrıca oylandı. ABD hayır oyu verdi; Birleşik Krallık çekimser kaldı. DHL listesi bu üç oylamayı birbirinin aynı üç satırla gösteriyor; sıralarını toplantı kaydından aldık.</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>Vote breakdown 13-1-1: S/PV.2580 para. 268 (PDF p. 30): second operative paragraph of S/17172 (separate vote); 13 in favour, 1 against (United States), 1 abstaining (United Kingdom). The three lines in the DHL list are identical; the identifiers were assigned in the order of the votes at the meeting.</t>
+          <t>The second operative paragraph of S/17172 was put to a separate vote. The United States voted against; the United Kingdom abstained. The DHL list shows these three votes as identical lines; we took their order from the meeting record.</t>
         </is>
       </c>
     </row>
@@ -17029,7 +16441,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Namibya'daki durum</t>
+          <t>Namibya’daki durum</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -17115,7 +16527,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Ortadoğu'daki durum</t>
+          <t>Ortadoğu’daki durum</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -17287,7 +16699,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Suriye'nin Güvenlik Konseyi Başkanı'na gönderdiği 4 Şubat 1986 tarihli mektup</t>
+          <t>Suriye’nin Güvenlik Konseyi Başkanı’na gönderdiği 4 Şubat 1986 tarihli mektup</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -17373,7 +16785,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Libya, Burkina Faso, Suriye ve Umman'ın Güvenlik Konseyi Başkanı'na gönderdiği 15 Nisan 1986 tarihli mektuplar</t>
+          <t>Libya, Burkina Faso, Suriye ve Umman’ın Güvenlik Konseyi Başkanı’na gönderdiği 15 Nisan 1986 tarihli mektuplar</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -17459,7 +16871,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Afrika'nın güneyindeki durum</t>
+          <t>Afrika’nın güneyindeki durum</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -17545,7 +16957,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Angola'nın Güney Afrika'ya karşı şikâyeti</t>
+          <t>Angola’nın Güney Afrika’ya karşı şikâyeti</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -17631,7 +17043,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Nikaragua'nın Güvenlik Konseyi Başkanı'na gönderdiği 22 Temmuz 1986 tarihli mektup</t>
+          <t>Nikaragua’nın Güvenlik Konseyi Başkanı’na gönderdiği 22 Temmuz 1986 tarihli mektup</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -17717,7 +17129,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Nikaragua'nın Güvenlik Konseyi Başkanı'na gönderdiği 17 Ekim 1986 tarihli mektup</t>
+          <t>Nikaragua’nın Güvenlik Konseyi Başkanı’na gönderdiği 17 Ekim 1986 tarihli mektup</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -17889,7 +17301,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Namibya'daki durum</t>
+          <t>Namibya’daki durum</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -17975,7 +17387,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Ortadoğu'daki durum</t>
+          <t>Ortadoğu’daki durum</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -18319,7 +17731,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Ortadoğu'daki durum</t>
+          <t>Ortadoğu’daki durum</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -18405,7 +17817,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Ortadoğu'daki durum</t>
+          <t>Ortadoğu’daki durum</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -18491,7 +17903,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Libya ve Bahreyn'in Güvenlik Konseyi Başkanı'na gönderdiği 4 Ocak 1989 tarihli mektuplar</t>
+          <t>Libya ve Bahreyn’in Güvenlik Konseyi Başkanı’na gönderdiği 4 Ocak 1989 tarihli mektuplar</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -18835,7 +18247,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Panama'daki durum</t>
+          <t>Panama’daki durum</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -18921,7 +18333,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Nikaragua'nın Güvenlik Konseyi Başkanı'na gönderdiği 3 Ocak 1990 tarihli mektup</t>
+          <t>Nikaragua’nın Güvenlik Konseyi Başkanı’na gönderdiği 3 Ocak 1990 tarihli mektup</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -19093,7 +18505,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Kıbrıs'taki durum</t>
+          <t>Kıbrıs’taki durum</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -19179,7 +18591,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Bosna-Hersek Cumhuriyeti'ndeki durum</t>
+          <t>Bosna-Hersek Cumhuriyeti’ndeki durum</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -19339,12 +18751,12 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>scprocedure tarihi 1995-09-17. Tarih farkı 4 ay. | Referans tablodaki tarih 1995-09-17; oylama günü toplantı kaydına göre 1995-05-17, DHL ile aynı. | S/PV.3538: toplantı 17 Mayıs 1995 Çarşamba 18.15-19.25; oylama PDF s. 6. Gece yarısı geçilmedi. Doğru tarihi DHL veriyor; referans tablodaki '17 Sept. 1995' ay hatası.</t>
+          <t>Oylama 17 Mayıs 1995’te yapıldı (S/PV.3538). Referans tabloda ay yanlış, 17 Eylül 1995 yazıyor.</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>scprocedure date 1995-09-17. Date difference 4 months. | Date in the reference table 1995-09-17; voting day according to the meeting record 1995-05-17, the same as DHL. | S/PV.3538: meeting on Wednesday, 17 May 1995, 18.15-19.25; vote PDF p. 6. Midnight was not passed. DHL gives the correct date; '17 Sept. 1995' in the reference table is an error in the month.</t>
+          <t>The vote took place on 17 May 1995 (S/PV.3538). The reference table gives the wrong month, 17 September 1995.</t>
         </is>
       </c>
     </row>
@@ -19371,7 +18783,7 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Genel Sekreter'in atanması</t>
+          <t>Genel Sekreter’in atanması</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -19426,12 +18838,12 @@
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>Kapalı oturum: veto eden üye resmi bildiride yok, kaynak tarafından atfedilmiş.</t>
+          <t>Oturum kapalıydı. Resmî bildiri veto eden üyeyi adlandırmıyor; adı DHL listesi veriyor.</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>Private meeting: the vetoing member is not named in the official communiqué; the attribution is the source's.</t>
+          <t>The meeting was private. The official communiqué does not name the vetoing member; the DHL list does.</t>
         </is>
       </c>
     </row>
@@ -19716,7 +19128,7 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Eski Yugoslav Makedonya Cumhuriyeti'ndeki durum</t>
+          <t>Eski Yugoslav Makedonya Cumhuriyeti’ndeki durum</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -19802,7 +19214,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Filistin meselesi dahil Ortadoğu'daki durum</t>
+          <t>Filistin meselesi dâhil Ortadoğu’daki durum</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -19866,12 +19278,12 @@
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>Kaynakta tarih aralığı var; oylama günü toplantı kaydından doğrulanmalı.</t>
+          <t>DHL listesi bu oylamanın tarihini bir aralık olarak veriyor.</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>The source gives a date range; the voting day is to be verified from the meeting record.</t>
+          <t>The DHL list gives the date of this vote as a range.</t>
         </is>
       </c>
     </row>
@@ -19898,7 +19310,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Filistin meselesi dahil Ortadoğu'daki durum</t>
+          <t>Filistin meselesi dâhil Ortadoğu’daki durum</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -19962,12 +19374,12 @@
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>Kaynakta tarih aralığı var; oylama günü toplantı kaydından doğrulanmalı.</t>
+          <t>DHL listesi bu oylamanın tarihini bir aralık olarak veriyor.</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>The source gives a date range; the voting day is to be verified from the meeting record.</t>
+          <t>The DHL list gives the date of this vote as a range.</t>
         </is>
       </c>
     </row>
@@ -19994,7 +19406,7 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Bosna-Hersek'teki durum</t>
+          <t>Bosna-Hersek’teki durum</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
@@ -20080,7 +19492,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Filistin meselesi dahil Ortadoğu'daki durum</t>
+          <t>Filistin meselesi dâhil Ortadoğu’daki durum</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -20166,7 +19578,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Filistin meselesi dahil Ortadoğu'daki durum</t>
+          <t>Filistin meselesi dâhil Ortadoğu’daki durum</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -20252,7 +19664,7 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Filistin meselesi dahil Ortadoğu'daki durum</t>
+          <t>Filistin meselesi dâhil Ortadoğu’daki durum</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
@@ -20338,7 +19750,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Filistin meselesi dahil Ortadoğu durumu</t>
+          <t>Filistin meselesi dâhil Ortadoğu’daki durum</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
@@ -20510,7 +19922,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Filistin meselesi dahil Ortadoğu durumu</t>
+          <t>Filistin meselesi dâhil Ortadoğu’daki durum</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -20596,7 +20008,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Filistin meselesi dahil Ortadoğu durumu</t>
+          <t>Filistin meselesi dâhil Ortadoğu’daki durum</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
@@ -20682,7 +20094,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Filistin meselesi dahil Ortadoğu durumu</t>
+          <t>Filistin meselesi dâhil Ortadoğu’daki durum</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -21026,7 +20438,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Filistin meselesi dahil Ortadoğu durumu</t>
+          <t>Filistin meselesi dâhil Ortadoğu’daki durum</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -21112,7 +20524,7 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Ortadoğu: Suriye</t>
+          <t>Ortadoğu’daki durum: Suriye</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -21198,7 +20610,7 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Ortadoğu: Suriye</t>
+          <t>Ortadoğu’daki durum: Suriye</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -21284,7 +20696,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Ortadoğu: Suriye</t>
+          <t>Ortadoğu’daki durum: Suriye</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -21370,7 +20782,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Ukrayna'nın BM Daimi Temsilcisi'nin Güvenlik Konseyi Başkanı'na hitaben yazdığı 28 Şubat 2014 tarihli mektup (S/2014/136)</t>
+          <t>Ukrayna’nın BM Daimi Temsilcisi’nin Güvenlik Konseyi Başkanı’na hitaben yazdığı 28 Şubat 2014 tarihli mektup (S/2014/136)</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -21456,7 +20868,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Ortadoğu: Suriye</t>
+          <t>Ortadoğu’daki durum: Suriye</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
@@ -21542,7 +20954,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Bosna-Hersek'teki durum</t>
+          <t>Bosna-Hersek’teki durum</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
@@ -21621,12 +21033,12 @@
       </c>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>Oy dağılımı 10-1-4: S/PV.7481 PDF s. 7: S/2015/508; 10 lehte, 1 aleyhte (Rusya), 4 çekimser (Angola, Çin, Nijerya, Venezuela). | Referans tablo (Tablo 4, #224) oy dağılımını 11-1-4 veriyor; toplantı kaydı esas alındı.</t>
+          <t>Rusya Federasyonu hayır oyu verdi; Angola, Çin, Nijerya ve Venezuela çekimser kaldı. | Referans tablo oyu 11-1-4 veriyor; biz toplantı kaydındaki 10-1-4 sonucunu aldık (Tablo 4, #224).</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
         <is>
-          <t>Vote breakdown 10-1-4: S/PV.7481 PDF p. 7: S/2015/508; 10 in favour, 1 against (Russia), 4 abstaining (Angola, China, Nigeria, Venezuela). | The reference table (Table 4, #224) gives the vote breakdown as 11-1-4; the meeting record was followed.</t>
+          <t>The Russian Federation voted against; Angola, China, Nigeria and Venezuela abstained. | The reference table gives 11-1-4; we follow the meeting record, which gives 10-1-4 (Table 4, #224).</t>
         </is>
       </c>
     </row>
@@ -21653,7 +21065,7 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Ukrayna'nın BM Daimi Temsilcisi'nin Güvenlik Konseyi Başkanı'na hitaben yazdığı 28 Şubat 2014 tarihli mektup (S/2014/136)</t>
+          <t>Ukrayna’nın BM Daimi Temsilcisi’nin Güvenlik Konseyi Başkanı’na hitaben yazdığı 28 Şubat 2014 tarihli mektup (S/2014/136)</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
@@ -21739,7 +21151,7 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Ortadoğu</t>
+          <t>Ortadoğu’daki durum</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
@@ -21825,7 +21237,7 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Ortadoğu</t>
+          <t>Ortadoğu’daki durum</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
@@ -21911,7 +21323,7 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Ortadoğu</t>
+          <t>Ortadoğu’daki durum</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
@@ -21997,7 +21409,7 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Ortadoğu</t>
+          <t>Ortadoğu’daki durum</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
@@ -22083,7 +21495,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Ortadoğu</t>
+          <t>Ortadoğu’daki durum</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
@@ -22169,7 +21581,7 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Ortadoğu</t>
+          <t>Ortadoğu’daki durum</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
@@ -22255,7 +21667,7 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Ortadoğu</t>
+          <t>Ortadoğu’daki durum</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
@@ -22341,7 +21753,7 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Filistin meselesi dahil Ortadoğu durumu</t>
+          <t>Filistin meselesi dâhil Ortadoğu’daki durum</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
@@ -22427,7 +21839,7 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Ortadoğu</t>
+          <t>Ortadoğu’daki durum</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
@@ -22513,7 +21925,7 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Ortadoğu</t>
+          <t>Ortadoğu’daki durum</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
@@ -22599,7 +22011,7 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Filistin meselesi dahil Ortadoğu durumu</t>
+          <t>Filistin meselesi dâhil Ortadoğu’daki durum</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
@@ -22685,7 +22097,7 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Venezuela Bolivarcı Cumhuriyeti'ndeki durum</t>
+          <t>Venezuela Bolivarcı Cumhuriyeti’ndeki durum</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
@@ -22771,7 +22183,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Ortadoğu'daki durum</t>
+          <t>Ortadoğu’daki durum</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
@@ -22857,7 +22269,7 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Ortadoğu'daki durum</t>
+          <t>Ortadoğu’daki durum</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
@@ -22943,7 +22355,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Ortadoğu'daki durum</t>
+          <t>Ortadoğu’daki durum</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
@@ -23024,7 +22436,7 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Ortadoğu'daki durum</t>
+          <t>Ortadoğu’daki durum</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
@@ -23265,12 +22677,12 @@
       </c>
       <c r="Z244" t="inlineStr">
         <is>
-          <t>Oy dağılımı 12-2-1: S/PV.8926 PDF s. 5: S/2021/990; 12 lehte, 2 aleyhte (Hindistan, Rusya), 1 çekimser (Çin). | Referans tablo (Tablo 4, #243) oy dağılımını 13-2-1 veriyor; toplantı kaydı esas alındı.</t>
+          <t>Hindistan ve Rusya Federasyonu hayır oyu verdi; Çin çekimser kaldı. | Referans tablo oyu 13-2-1 veriyor; biz toplantı kaydındaki 12-2-1 sonucunu aldık (Tablo 4, #243).</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
         <is>
-          <t>Vote breakdown 12-2-1: S/PV.8926 PDF p. 5: S/2021/990; 12 in favour, 2 against (India, Russia), 1 abstaining (China). | The reference table (Table 4, #243) gives the vote breakdown as 13-2-1; the meeting record was followed.</t>
+          <t>India and the Russian Federation voted against; China abstained. | The reference table gives 13-2-1; we follow the meeting record, which gives 12-2-1 (Table 4, #243).</t>
         </is>
       </c>
     </row>
@@ -23297,7 +22709,7 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Ukrayna'nın BM Daimi Temsilcisi'nin Güvenlik Konseyi Başkanı'na hitaben yazdığı 28 Şubat 2014 tarihli mektup (S/2014/136)</t>
+          <t>Ukrayna’nın BM Daimi Temsilcisi’nin Güvenlik Konseyi Başkanı’na hitaben yazdığı 28 Şubat 2014 tarihli mektup (S/2014/136)</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
@@ -23479,7 +22891,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Ortadoğu'daki durum</t>
+          <t>Ortadoğu’daki durum</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
@@ -23575,7 +22987,7 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Ukrayna'nın barış ve güvenliğinin korunması</t>
+          <t>Ukrayna’nın barış ve güvenliğinin korunması</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
@@ -23671,7 +23083,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Ortadoğu'daki durum</t>
+          <t>Ortadoğu’daki durum</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
@@ -23767,7 +23179,7 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Mali'deki durum</t>
+          <t>Mali’deki durum</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
@@ -23863,7 +23275,7 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Filistin meselesi dahil Ortadoğu'daki durum</t>
+          <t>Filistin meselesi dâhil Ortadoğu’daki durum</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
@@ -23959,7 +23371,7 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Filistin meselesi dahil Ortadoğu'daki durum</t>
+          <t>Filistin meselesi dâhil Ortadoğu’daki durum</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
@@ -24055,7 +23467,7 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Filistin meselesi dahil Ortadoğu'daki durum</t>
+          <t>Filistin meselesi dâhil Ortadoğu’daki durum</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
@@ -24151,7 +23563,7 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Filistin meselesi dahil Ortadoğu'daki durum</t>
+          <t>Filistin meselesi dâhil Ortadoğu’daki durum</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
@@ -24225,12 +23637,12 @@
       </c>
       <c r="Z254" t="inlineStr">
         <is>
-          <t>Kaynakta 'oral amendment': veto, taslağa toplantıda sözlü olarak önerilen değişikliğe yöneliktir.</t>
+          <t>Veto, toplantıda taslağa sözlü olarak önerilen bir değişikliğe karşı kullanıldı.</t>
         </is>
       </c>
       <c r="AA254" t="inlineStr">
         <is>
-          <t>The source says 'oral amendment': the veto concerns an amendment to the draft proposed orally at the meeting.</t>
+          <t>The veto was cast against an oral amendment to the draft, proposed at the meeting.</t>
         </is>
       </c>
     </row>
@@ -24257,7 +23669,7 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Filistin meselesi dahil Ortadoğu'daki durum</t>
+          <t>Filistin meselesi dâhil Ortadoğu’daki durum</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
@@ -24353,7 +23765,7 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Filistin meselesi dahil Ortadoğu'daki durum</t>
+          <t>Filistin meselesi dâhil Ortadoğu’daki durum</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
@@ -24742,7 +24154,7 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Genel Sekreter'in Sudan ve Güney Sudan hakkındaki raporları</t>
+          <t>Genel Sekreter’in Sudan ve Güney Sudan hakkındaki raporları</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
@@ -24838,7 +24250,7 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Filistin meselesi dahil Ortadoğu'daki durum</t>
+          <t>Filistin meselesi dâhil Ortadoğu’daki durum</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
@@ -24934,7 +24346,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Ukrayna'nın barış ve güvenliğinin korunması</t>
+          <t>Ukrayna’nın barış ve güvenliğinin korunması</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
@@ -25023,12 +24435,12 @@
       </c>
       <c r="Z262" t="inlineStr">
         <is>
-          <t>DHL iki ayrı değişiklik önergesine yönelik iki vetoyu tek satırda gösteriyor | Oy dağılımı 9-1-5: S/PV.9866 PDF s. 6: Danimarka, Fransa, Yunanistan, Slovenya ve Birleşik Krallık'ın yeni üçüncü giriş paragrafı ekleyen değişiklik önergesi S/2025/115; 9 lehte, 1 aleyhte (Rusya), 5 çekimser (Çin, Guyana, Panama, Pakistan, ABD).</t>
+          <t>DHL listesi iki ayrı değişiklik önergesine verilen iki vetoyu tek satırda gösteriyor. | Danimarka, Fransa, Yunanistan, Slovenya ve Birleşik Krallık’ın yeni bir üçüncü giriş paragrafı ekleyen değişiklik önergesine (S/2025/115) Rusya Federasyonu hayır oyu verdi; Çin, Guyana, Panama, Pakistan ve ABD çekimser kaldı.</t>
         </is>
       </c>
       <c r="AA262" t="inlineStr">
         <is>
-          <t>The DHL list shows two vetoes of two separate amendments on a single line | Vote breakdown 9-1-5: S/PV.9866 PDF p. 6: amendment S/2025/115 by Denmark, France, Greece, Slovenia and the United Kingdom adding a new third preambular paragraph; 9 in favour, 1 against (Russia), 5 abstaining (China, Guyana, Panama, Pakistan, United States).</t>
+          <t>The DHL list shows the two vetoes of two separate amendments on a single line. | The Russian Federation voted against the amendment by Denmark, France, Greece, Slovenia and the United Kingdom adding a new third preambular paragraph (S/2025/115); China, Guyana, Panama, Pakistan and the United States abstained.</t>
         </is>
       </c>
     </row>
@@ -25055,7 +24467,7 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Ukrayna'nın barış ve güvenliğinin korunması</t>
+          <t>Ukrayna’nın barış ve güvenliğinin korunması</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
@@ -25144,12 +24556,12 @@
       </c>
       <c r="Z263" t="inlineStr">
         <is>
-          <t>DHL iki ayrı değişiklik önergesine yönelik iki vetoyu tek satırda gösteriyor | Oy dağılımı 11-1-3: S/PV.9866 PDF s. 7: aynı ülkelerin birinci karar paragrafına değişiklik önergesi S/2025/116; 11 lehte, 1 aleyhte (Rusya), 3 çekimser (Panama, Pakistan, ABD).</t>
+          <t>DHL listesi iki ayrı değişiklik önergesine verilen iki vetoyu tek satırda gösteriyor. | Aynı ülkelerin birinci karar paragrafına önerdiği değişikliğe (S/2025/116) Rusya Federasyonu hayır oyu verdi; Panama, Pakistan ve ABD çekimser kaldı.</t>
         </is>
       </c>
       <c r="AA263" t="inlineStr">
         <is>
-          <t>The DHL list shows two vetoes of two separate amendments on a single line | Vote breakdown 11-1-3: S/PV.9866 PDF p. 7: amendment S/2025/116 by the same countries to the first operative paragraph; 11 in favour, 1 against (Russia), 3 abstaining (Panama, Pakistan, United States).</t>
+          <t>The DHL list shows the two vetoes of two separate amendments on a single line. | The Russian Federation voted against the amendment by the same countries to the first operative paragraph (S/2025/116); Panama, Pakistan and the United States abstained.</t>
         </is>
       </c>
     </row>
@@ -25176,7 +24588,7 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Filistin meselesi dahil Ortadoğu'daki durum</t>
+          <t>Filistin meselesi dâhil Ortadoğu’daki durum</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
@@ -25272,7 +24684,7 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Filistin meselesi dahil Ortadoğu'daki durum</t>
+          <t>Filistin meselesi dâhil Ortadoğu’daki durum</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
@@ -25368,7 +24780,7 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Ortadoğu'daki durum</t>
+          <t>Ortadoğu’daki durum</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
@@ -25457,12 +24869,12 @@
       </c>
       <c r="Z266" t="inlineStr">
         <is>
-          <t>Oy dağılımı 11-2-2: DHL listesinde oy dağılımı yok, referans tablo bu tarihi kapsamıyor. S/PV.10130 s. 4: S/2026/273 (Bahreyn, Ürdün, Kuveyt, Katar, Suudi Arabistan ve BAE taslağı, Hürmüz Boğazı) 11 lehte, 2 aleyhte (Çin, Rusya Federasyonu), 2 çekimser (Kolombiya, Pakistan). Kayıtta Başkan 'bir daimi üyenin ret oyu nedeniyle' diyor; oy listesinde iki daimi üye aleyhte. Basın bülteni SC/16330 (https://press.un.org/en/2026/sc16330.doc.htm) doğrulanamadı.</t>
+          <t>DHL listesi oy sayılarını vermiyor; referans tablo bu tarihten önce bitiyor. Bahreyn, Ürdün, Kuveyt, Katar, Suudi Arabistan ve BAE’nin Hürmüz Boğazı taslağına (S/2026/273) Çin ve Rusya Federasyonu hayır oyu verdi; Kolombiya ve Pakistan çekimser kaldı. Kayıtta Başkan “bir daimî üyenin ret oyu nedeniyle” diyor; oy listesinde iki daimî üye hayır oyu verdi.</t>
         </is>
       </c>
       <c r="AA266" t="inlineStr">
         <is>
-          <t>Vote breakdown 11-2-2: The DHL list has no vote breakdown and the reference table does not cover this date. S/PV.10130 p. 4: S/2026/273 (draft by Bahrain, Jordan, Kuwait, Qatar, Saudi Arabia and the UAE, Strait of Hormuz) 11 in favour, 2 against (China, Russian Federation), 2 abstaining (Colombia, Pakistan). In the record the President refers to the negative vote of a permanent member; in the voting list two permanent members voted against. Press release SC/16330 (https://press.un.org/en/2026/sc16330.doc.htm) could not be verified.</t>
+          <t>The DHL list gives no vote figures, and the reference table ends before this date. China and the Russian Federation voted against the draft of Bahrain, Jordan, Kuwait, Qatar, Saudi Arabia and the UAE on the Strait of Hormuz (S/2026/273); Colombia and Pakistan abstained. In the record the President refers to the negative vote of a permanent member; in the voting list two permanent members voted against.</t>
         </is>
       </c>
     </row>
@@ -25578,12 +24990,12 @@
       </c>
       <c r="Z267" t="inlineStr">
         <is>
-          <t>DHL listesinde ve referans tabloda henüz yok. S/PV.10224 s. 4: S/2026/740 (ABD taslağı) 11 lehte, 2 aleyhte (Çin, Rusya Federasyonu), 2 çekimser (Pakistan, Somali); kabul edilmedi. Taslak, 1929 (2010) sayılı kararın 29. paragrafıyla kurulan ve İran yaptırımlarını izleyen Uzmanlar Paneli'nin görevini uzatıyordu. Toplantı başında gündemin kabulü 11-2-2 usul oylamasıyla geçti (usul oylamasında veto yoktur). Basın bülteni SC/16455 (https://press.un.org/en/2026/sc16455.doc.htm) aynı sonucu veriyor.</t>
+          <t>Kayıt DHL listesinde ve referans tabloda henüz yok. ABD taslağına (S/2026/740) Çin ve Rusya Federasyonu hayır oyu verdi; Pakistan ve Somali çekimser kaldı. Taslak, 1929 (2010) sayılı kararın 29. paragrafıyla kurulan ve İran yaptırımlarını izleyen Uzmanlar Panelinin görevini uzatıyordu. Gündem toplantının başında 11 evet, 2 hayır, 2 çekimser oyla kabul edildi; bu bir usul oylamasıydı ve ret oyu veto sayılmaz. Basın bülteni SC/16455 aynı sonucu veriyor.</t>
         </is>
       </c>
       <c r="AA267" t="inlineStr">
         <is>
-          <t>Not yet in the DHL list or the reference table. S/PV.10224 p. 4: S/2026/740 (United States draft) 11 in favour, 2 against (China, Russian Federation), 2 abstaining (Pakistan, Somalia); not adopted. The draft would have extended the mandate of the Panel of Experts established by paragraph 29 of resolution 1929 (2010) to monitor the sanctions on Iran. At the start of the meeting the agenda was adopted by a procedural vote of 11-2-2 (there is no veto in procedural votes). Press release SC/16455 (https://press.un.org/en/2026/sc16455.doc.htm) gives the same result.</t>
+          <t>Not yet in the DHL list or the reference table. China and the Russian Federation voted against the United States draft (S/2026/740); Pakistan and Somalia abstained. The draft would have extended the mandate of the Panel of Experts established by paragraph 29 of resolution 1929 (2010) to monitor the sanctions on Iran. The agenda was adopted at the start of the meeting with 11 in favour, 2 against, 2 abstaining; as a procedural vote, it was not subject to the veto. Press release SC/16455 gives the same result.</t>
         </is>
       </c>
     </row>
@@ -25591,4 +25003,1105 @@
   <autoFilter ref="A1:AA267"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>dosya</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>sutun</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>tip</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>bos_anlami</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>bos_anlami_en</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>degerler</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>aciklama_tr</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>aciklama_en</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>vetolar.csv</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>metin</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Boş olmaz</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Never empty</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Kaydın sabit anahtarı, V-YYYY-AA-GG-n biçiminde. İçindeki tarih kaydın ilk oluşturulduğu andaki DHL tarihidir; vetonun tarihi tarih sütunundadır.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Stable record key in the form V-YYYY-MM-DD-n. The date inside it is the DHL date at the time the record was first created; the date of the veto is in the tarih column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>vetolar.csv</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>tarih</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>tarih (YYYY-AA-GG)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Boş olmaz</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Never empty</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Oylamanın yapıldığı takvim günü. Gece yarısını geçen toplantılarda toplantı kaydının başlığındaki tarihten farklı olabilir.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Calendar day of the vote. For meetings that ran past midnight it can differ from the date in the heading of the meeting record.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>vetolar.csv</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>tarih_ham</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>metin</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Boş olmaz</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Never empty</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Kaynağın verdiği tarih, kaynaktaki yazımıyla. Örnekler: 13 March 1953, 3-4 December 1960.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>The date as the source gives it, in the source's wording. Examples: 13 March 1953, 3-4 December 1960.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>vetolar.csv</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>referans_tarih</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>tarih (YYYY-AA-GG)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>İki kaynağın tarihi aynı</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>The two sources give the same date</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Referans tablonun (scprocedure.org, Tablo 4) verdiği tarih. Yalnızca iki kaynağın tarihinin ayrıştığı 7 kayıtta doludur.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>The date given by the reference table (scprocedure.org, Table 4). Filled only in the 7 records where the two sources give different dates. Empty means both sources give the same date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>vetolar.csv</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>gundem_maddesi</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>metin</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Boş olmaz</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Never empty</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Gündem maddesinin BM'deki İngilizce başlığı.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Title of the agenda item as the UN gives it, in English.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>vetolar.csv</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>gundem_tr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>metin</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Boş olmaz</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Never empty</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Gündem başlığının sadık Türkçe çevirisi.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Faithful Turkish translation of the agenda item title.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>vetolar.csv</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>konu_kategorisi</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>kod</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Boş olmaz</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Never empty</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Filistin ve Arap-İsrail meselesi | Lübnan | Suriye | Diğer Ortadoğu ve Kuzey Afrika | Kıbrıs | Ukrayna | Diğer Avrupa | Güney Afrika, Namibya ve Rodezya | Diğer Afrika | Latin Amerika ve Karayipler | Asya | Silahsızlanma ve askerî gerilimler | Üyelik başvuruları | Genel Sekreter seçimi | Tematik konular</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Ana konu. Her veto tek bir ana konuya atanır ve konu sayımları yalnızca bu sütunu kullanır.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Main topic, in Turkish. Each veto has exactly one main topic, and topic counts use only this column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>vetolar.csv</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ikincil_konular</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>liste (; ile ayrılır)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>İkincil konu yok</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>No secondary topic</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>konu_kategorisi ile aynı değerler</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Ana konu dışında kaydın değdiği konular. Filtrelemede kullanılır, hiçbir sayıma girmez.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Other topics the record touches besides the main topic. Used for filtering and not counted anywhere. Empty means there is no secondary topic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>vetolar.csv</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>bolge</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>kod</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Boş olmaz</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Never empty</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ortadoğu ve Kuzey Afrika | Avrupa | Afrika | Asya ve Pasifik | Latin Amerika ve Karayipler | Küresel</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Gündem maddesinin bölgesi. Küresel, belirli bir bölgeye bağlı olmayan gündem maddeleridir.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Region of the agenda item, in Turkish. In the order of the values column: Middle East and North Africa, Europe, Africa, Asia and the Pacific, Latin America and the Caribbean, and Global. Global covers agenda items not tied to one region.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>vetolar.csv</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>veto_eden_uyeler</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>liste (; ile ayrılır)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Boş olmaz</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Never empty</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>USA | RUS | SSCB | CHN | GBR | FRA</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Veto eden daimî üye ya da üyeler. SSCB, Rusya Federasyonu'ndan (RUS) ayrı kodlanır. 25 Ekim 1971'den önceki CHN vetoları Çin Cumhuriyeti'ne aittir.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>The permanent member or members that cast the veto. SSCB is the Soviet Union, coded separately from RUS, the Russian Federation. CHN vetoes before 25 October 1971 belong to the Republic of China.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>vetolar.csv</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>kapali_oturum</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>True/False</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Boş olmaz</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Never empty</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>True | False</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>True, vetonun kapalı oturumda kullanıldığını gösterir. Resmî bildiri veto eden üyeyi adlandırmaz, üyeyi DHL listesi verir. Bu kayıtlarda oy dağılımı yoktur.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>True marks a veto cast in a private meeting. The official communiqué does not name the vetoing member; the DHL list does. These records have no vote breakdown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>vetolar.csv</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>oy_lehte</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>tam sayı</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Oy dağılımı yok (kapalı oturumdaki 2 kayıt)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>No vote breakdown (the 2 records from private meetings)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Taslağın lehine verilen oy sayısı.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Number of votes in favour of the draft. Empty when there is no vote breakdown, as in the 2 private-meeting records.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>vetolar.csv</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>oy_aleyhte</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>tam sayı</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Oy dağılımı yok (kapalı oturumdaki 2 kayıt)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>No vote breakdown (the 2 records from private meetings)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Taslağın aleyhine verilen oy sayısı. Daimî üyelerin ret oyları da bu sayıya girer.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Number of votes against the draft, including the negative votes of permanent members. Empty when there is no vote breakdown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>vetolar.csv</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>oy_cekimser</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>tam sayı</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Oy dağılımı yok (kapalı oturumdaki 2 kayıt)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>No vote breakdown (the 2 records from private meetings)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Çekimser kalan üye sayısı.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Number of abstentions. Empty when there is no vote breakdown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>vetolar.csv</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>taslak_belgeler</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>liste (; ile ayrılır)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Taslak ayrı belge olarak yayımlanmadı; taslak_kaynagi toplanti_kaydi</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>The draft was not issued as a separate document; taslak_kaynagi is toplanti_kaydi</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Veto edilen karar taslağının ve varsa değişiklik önergesinin belge kodları (S/…).</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Document symbols of the vetoed draft resolution and, where there is one, the amendment (S/…). Empty when the draft was not issued as a separate document.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>vetolar.csv</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>toplanti_kayitlari</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>liste (; ile ayrılır)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Kaynakta toplantı kaydı kodu yok (2020’deki 3 kayıt)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>The source gives no meeting record symbol (the 3 records from 2020)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Oylamanın geçtiği toplantının kaydı (S/PV.…).</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Symbol of the meeting record of the vote (S/PV.…). Empty in 3 records from 2020, for which the source gives no meeting record.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>vetolar.csv</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>kismi_veto_suphesi</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>True/False</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Boş olmaz</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Never empty</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>True | False</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>True, vetonun taslağın bütününe değil, bir değişiklik önergesine ya da taslağın bir bölümüne yapılan ayrı oylamada kullanıldığını gösterir. Bölüm bir paragraf, cümle ya da kelime olabilir.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>True marks a veto cast in a separate vote on an amendment or on part of the draft, not on the draft as a whole. The part can be a paragraph, a sentence or a word.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>vetolar.csv</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>on_soru_vetosu</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>True/False</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Boş olmaz</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Never empty</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>True | False</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>True, vetonun bir meselenin usul meselesi sayılıp sayılmayacağına dair ön soru oylamasında kullanıldığını gösterir. Bu oylamaya çifte veto da denir.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>True marks a veto cast on the preliminary question of whether a matter is procedural, also called the double veto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>vetolar.csv</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>taslak_kaynagi</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>kod</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Boş olmaz</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Never empty</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>belge | toplanti_kaydi</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Taslağın nerede yer aldığı. belge, taslağın ayrı bir S/ belgesi olarak yayımlandığını gösterir. toplanti_kaydi, ayrı belge olmadığını ve önerinin toplantı kaydında yer aldığını gösterir.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Where the draft appears. belge means it was issued as a separate S/ document. toplanti_kaydi means there is no separate document and the proposal appears in the meeting record.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>vetolar.csv</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>toplanti_dogrulamasi</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>liste (; ile ayrılır)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Toplantı kaydından ayrı bir doğrulama yapılmadı</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Not checked separately against the meeting record</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Toplantı kaydından doğrulanan alanlar, alan: durum (kayıt, par. N, s. N) biçiminde. Alan tarih, oy ya da uye olur; durum dogrulandi ya da dogrulanamadi. Sayfa numarası PDF sayfasıdır, paragraf numarası varsa birincil atıf odur.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Fields checked against the meeting record, in the form field: status (record, par. N, s. N). The field is tarih for the date, oy for the vote breakdown or uye for the vetoing member. The status is dogrulandi when verified and dogrulanamadi when the record does not settle it. Page numbers are PDF pages; a paragraph number, where there is one, is the primary reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>vetolar.csv</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>genel_kurul_durum</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>kod</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Boş olmaz</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Never empty</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>yapildi | bekleniyor | kapsam_disi</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Vetodan sonra A/RES/76/262 uyarınca yapılan Genel Kurul tartışmasının durumu. kapsam_disi, vetonun 26 Nisan 2022'den önce olduğunu gösterir. yapildi, tartışmanın yapıldığını, bekleniyor ise henüz bir tartışma kaydı olmadığını gösterir.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Status of the General Assembly debate held after the veto under A/RES/76/262. kapsam_disi means the veto predates 26 April 2022. yapildi means the debate took place, and bekleniyor means no debate has been recorded yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>vetolar.csv</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ozel_rapor</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>metin</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Veto 26 Nisan 2022’den önce ya da rapor kayıtlı değil</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Veto before 26 April 2022, or no report recorded</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Güvenlik Konseyinin bu veto için Genel Kurula sunduğu özel raporun kodu (A/…).</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Symbol of the special report the Security Council submitted to the General Assembly on this veto (A/…). Empty for vetoes before 26 April 2022.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>vetolar.csv</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>genel_kurul_tartismalari</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>liste (; ile ayrılır)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Veto 26 Nisan 2022’den önce ya da tartışma kayıtlı değil</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Veto before 26 April 2022, or no debate recorded</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Bu vetoyu ele alan Genel Kurul tartışmalarının kimlikleri. Ayrıntılar genel_kurul_tartismalari.csv dosyasının tartisma_id sütunundadır.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>IDs of the General Assembly debates on this veto. Details are under tartisma_id in genel_kurul_tartismalari.csv. Empty for vetoes before 26 April 2022.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>vetolar.csv</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>duzeltme</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>metin</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Referans tabloyla mutabakatta kayıt değişmedi</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>The record did not change in reconciliation with the reference table</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Referans tabloyla mutabakatta kayda yapılan ekleme ya da değişiklik ve dayanağı. scprocedure #N, Tablo 4'teki satır numarasıdır.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Addition or change made to the record when it was reconciled with the reference table, and its basis, in Turkish. scprocedure #N is the row number in Table 4. Empty when reconciliation did not change the record.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>vetolar.csv</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>duzeltme_en</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>metin</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Referans tabloyla mutabakatta kayıt değişmedi</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>The record did not change in reconciliation with the reference table</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>duzeltme sütununun İngilizcesi.</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>English version of the duzeltme column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>vetolar.csv</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>notlar</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>liste (| ile ayrılır)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Kayda ait not yok</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>No note for the record</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Kayda ait notlar. Türkçe asıl metindir, birden fazla not | ile ayrılır.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Notes on the record in Turkish, which is the original text. Several notes are separated by |. Empty when the record has no notes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>vetolar.csv</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>notlar_en</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>liste (| ile ayrılır)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Kayda ait not yok</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>No note for the record</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>notlar sütunundaki notların aynı sıradaki İngilizceleri.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>English versions of the notes in the notlar column, in the same order.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H28"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>